--- a/data/resultado.xlsx
+++ b/data/resultado.xlsx
@@ -13847,11 +13847,11 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Incrementa tu Línea AQUÍ y participa en el sorteo hasta el 30/04. TyC.</t>
+          <t>Incrementa tu Línea AQUÍ y participa en el sorteo hasta el 31/05. TyC. 🎁</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>Gana un iPhone 17 Pro Max 🎁</t>
+          <t>Participa por un iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -13915,11 +13915,11 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hazlo HOY y participa en el sorteo por un iPhone 17 Pro Max. Aplican TyC.</t>
+          <t>Incrementa la línea de tu Tarjeta  y disfruta de más beneficios.</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
@@ -13983,11 +13983,11 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tienes hasta S/{S} disponibles en tu tarjeta. Actívalos y aprovecha más oportunidades.</t>
+          <t>Incrementa tu línea AQUÍ y aprovecha más oportunidades. Aplican TyC.</t>
         </is>
       </c>
       <c r="H201" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>Incrementa tu línea HOY 😎</t>
+          <t>Hasta MONTO para ti 😎</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Solicítala AQUÍ y aprovecha todos sus beneficios. 😎</t>
+          <t>Pide HOY una Tarjeta de Crédito adicional y participa por 1 iPhone 17 Pro Max. TyC.</t>
         </is>
       </c>
       <c r="H216" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>Tarjeta de Crédito Adicional 💳</t>
+          <t>Comparte tu línea y gana 😉</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Solicítala AQUÍ y aprovecha todos sus beneficios. 😎</t>
+          <t>Solicita AQUÍ una Tarjeta de Crédito Adicional y participa. TyC.</t>
         </is>
       </c>
       <c r="H217" t="n">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>Tarjeta de Crédito Adicional 💳</t>
+          <t>Un iPhone 17 Pro Max te espera 📱</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Aprovecha este beneficio de tu nueva tarjeta. Mejórala HOY.  TyC.</t>
+          <t>Solo mejora tu tarjeta HOY y entra al sorteo. Aplican TyC.</t>
         </is>
       </c>
       <c r="H239" t="n">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>"Recibe 2,000 Millas sin sorteos 💳"</t>
+          <t>Llévate un iPhone 17 Pro Max 😎</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>"Mejora tu tarjeta y gana 2,000 Millas Benefit. Aplican TyC."</t>
+          <t>Hazlo AQUÍ y participa por un iPhone 17 Pro Max. TyC.</t>
         </is>
       </c>
       <c r="H240" t="n">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>Solo por HOY ⏳ 💳</t>
+          <t>Mejora tu Tarjeta ⬆️🚀</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Mejora tu tarjeta AQUÍ y recíbelas por tu primer consumo. TyC.</t>
+          <t>Mejora tu tarjeta HOY y entra al sorteo de un iPhone 17 Pro Max. TyC.</t>
         </is>
       </c>
       <c r="H241" t="n">
@@ -16726,7 +16726,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>"2,000 Millas para lo que quieras 🛍️"</t>
+          <t>Pasa a otro nivel 📈</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">

--- a/data/resultado.xlsx
+++ b/data/resultado.xlsx
@@ -6655,7 +6655,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>"Gana 5,000 Millas ¡sin sorteos!"</t>
+          <t>interbank://internal/te-ofrecemos/incremento-linea/onboarding</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Abre tu Cuenta Millonaria y obtén un doble giro el próximo mes. Hazlo aquí. TyC</t>
+          <t>Multiplica tus opciones y gana el Premio Soñado con tu Cuenta Millonaria. Ábrela hoy. TyC.​</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>¡Gana con la Ruleta!</t>
+          <t>¡Depa + auto + viaje!</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Abre tu Cuenta Millonaria y obtén un doble giro el próximo mes. Hazlo aquí. TyC</t>
+          <t>Multiplica tus opciones y gana el Premio Soñado con tu Cuenta Millonaria. Ábrela hoy. TyC.​</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>¡Gana con la Ruleta!</t>
+          <t>¡Depa + auto + viaje!</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>¡Hoy tú eliges tu premio!</t>
+          <t>"Abre hoy tu Depósito a Plazo desde S/15,000 y elige uno, ¡sin sorteos!. Inicia &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Tu dinero crece de forma segura</t>
+          <t>¡Una tabla de quesos o audífonos!</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>"¡Sin sorteos! Abre hoy tu Depósito a Plazo desde S/15,000 y listo. Inicia &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
+          <t>"Abre hoy tu Depósito a Plazo desde S/15,000 y elige uno, ¡sin sorteos!. Inicia &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>¡Hoy tú eliges tu premio!</t>
+          <t>¡Una tabla de quesos o audífonos!</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>"¡Sin sorteos! Abre hoy tu Cuenta Súper Tasa desde S/15,000 y elige uno. Inicia &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
+          <t>"Abre hoy tu Cuenta Súper Tasa con S/15,000 y elígelo ¡sin sorteos! Inicia &lt;b&gt;aquí&lt;/b&gt;. Aplican TyC."</t>
         </is>
       </c>
       <c r="H107" t="n">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>¡Tus ahorros siguen creciendo!</t>
+          <t>¡Tenemos un regalo para ti!</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Solo traslada tu Cuenta Sueldo a Interbank y obtén este beneficio. Hazlo aquí. TyC</t>
+          <t>Recibe tu sueldo en Interbank y llévate un producto sin sorteos. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC.</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>¡Rappi Pro Black gratis!</t>
+          <t>¡Tu sueldo vale un regalo!</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Incrementa tu línea hasta en {S} y planea tu siguiente viaje. &lt;b&gt;Hazlo aquí&lt;/b&gt;.</t>
+          <t>Incrementa la línea de tu Tarjeta de Crédito hoy a {S} y participa. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC.</t>
         </is>
       </c>
       <c r="H151" t="n">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>¡Potencia tu Tarjeta de Crédito!</t>
+          <t>"Gana 5,000 Millas ¡sin sorteos!"</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>"Gana 5,000 Millas ¡sin sorteos!"</t>
+          <t>interbank://internal/te-ofrecemos/incremento-linea/onboarding</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Abre tu Cuenta Millonaria y obtén un doble giro el próximo mes. Hazlo aquí. TyC</t>
+          <t>Multiplica tus opciones y gana el Premio Soñado con tu Cuenta Millonaria. Ábrela hoy. TyC.​</t>
         </is>
       </c>
       <c r="H153" t="n">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>¡Gana con la Ruleta! ✨</t>
+          <t>¡Depa + auto + viaje!</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Abre tu Depósito a Plazo con hasta 4% TREA y gana. Hazlo aquí. TyC.</t>
+          <t>"Abre hoy tu Depósito a Plazo desde S/100,000 y elige uno ¡sin sorteos! Inicia &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
         </is>
       </c>
       <c r="H155" t="n">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>"¡Sin sorteos!, llévate un premio"</t>
+          <t>¡Set de ollas Tramontina o smarwatch!</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Abre tu Cuenta Súper Tasa con hasta 4.5% TREA y participa. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC.</t>
+          <t>"Abre hoy tu Cuenta Súper Tasa desde S/100,000 y elige uno, ¡sin sorteos! Inicia &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
         </is>
       </c>
       <c r="H159" t="n">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>¡Gana un premio sin sorteos!</t>
+          <t>¡Set de ollas Tramontina o smarwatch!</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Solo traslada tu Cuenta Sueldo a Interbank y obtén este beneficio. Hazlo aquí. TyC</t>
+          <t>Recibe tu sueldo en Interbank y llévate un producto sin sorteos. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC.</t>
         </is>
       </c>
       <c r="H161" t="n">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>¡Rappi Pro Black gratis!</t>
+          <t>¡Tu sueldo vale un regalo!</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Con hasta 50% dscto. con tu nueva Tarjeta de Crédito. Obtenla &lt;b&gt;aquí&lt;/b&gt;. TyC.</t>
+          <t>"Por tiempo limitado, obtén una Tarjeta de Crédito, úsala y gana sin sorteos. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
         </is>
       </c>
       <c r="H165" t="n">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>"¡Estos Días Interbank, engríe a Mamá!"</t>
+          <t>¡Hasta S/600 pueden ser tuyos!</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Con hasta 50% dscto. con tu nueva Tarjeta de Crédito. Obtenla &lt;b&gt;aquí&lt;/b&gt;. TyC.</t>
+          <t>"Por tiempo limitado, obtén una Tarjeta de Crédito, úsala y gana sin sorteos. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
         </is>
       </c>
       <c r="H166" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>"¡Estos Días Interbank, engríe a Mamá!"</t>
+          <t>¡Hasta S/600 pueden ser tuyos!</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Este mes accede a una mejor Tarjeta de Crédito. &lt;b&gt;Obtenla aquí.&lt;/b&gt;</t>
+          <t>"Tienes una mejora de tu Tarjeta de Crédito, obtenla hoy y participa. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
         </is>
       </c>
       <c r="H174" t="n">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>¡Buenas noticias!</t>
+          <t>"Gana 5,000 Millas ¡al instante!"</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Incrementa tu Línea AQUÍ y participa en el sorteo hasta el 30/04. TyC.</t>
+          <t>Incrementa tu Línea AQUÍ y participa en el sorteo hasta el 31/05. TyC. 🎁</t>
         </is>
       </c>
       <c r="H259" t="n">

--- a/data/resultado.xlsx
+++ b/data/resultado.xlsx
@@ -7851,7 +7851,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Recibe tu sueldo en Interbank y llévate un producto sin sorteos. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC.</t>
+          <t>"Abre tu cuenta, recibe tu sueldo en Interbank y llévate un producto sin sorteos.  Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Incrementa tu línea AQUÍ y aprovecha más oportunidades. Aplican TyC.</t>
+          <t>"Incremento tu línea hoy "</t>
         </is>
       </c>
       <c r="H201" t="n">

--- a/data/resultado.xlsx
+++ b/data/resultado.xlsx
@@ -6491,7 +6491,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Prepara las maletas y disfruta tu viaje sin preocupaciones.</t>
+          <t>Disfruta de tu viaje con tranquilidad desde $2 al día.</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -6500,7 +6500,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/577e06a7-661b-41ce-b69a-cfa538fe5618.png</t>
+          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/92790487-6957-4bae-9f19-2ecae7fa69f6.png</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Incrementa tu línea hasta en {S} y planea tu siguiente viaje. &lt;b&gt;Hazlo aquí&lt;/b&gt;.</t>
+          <t>Aumenta tu línea a S/{S} y entra al sorteo de un iPhone 17 Pro Max. Hazlo aquí hoy. TyC.</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>¡Potencia tu Tarjeta de Crédito!</t>
+          <t>Tu tarjeta puede darte más</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Incrementa tu línea hasta en {S} y planea tu siguiente viaje. &lt;b&gt;Hazlo aquí&lt;/b&gt;.</t>
+          <t>Aumenta tu línea a S/{S} y entra al sorteo de un iPhone 17 Pro Max. Hazlo aquí hoy. TyC.</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>¡Potencia tu Tarjeta de Crédito!</t>
+          <t>Tu tarjeta puede darte más</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>"👉 Obtén tu Extracash de S/{S} y gana 3,000 Millas sin sorteos. TyC. Hazlo aquí"</t>
+          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>¡Un beneficio pensado para ti!</t>
+          <t>¡Tu Extracash puede llevarte a México!</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>"👉 Obtén tu Extracash de S/{S} y gana 3,000 Millas sin sorteos. TyC. Hazlo aquí"</t>
+          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>¡Un beneficio pensado para ti!</t>
+          <t>¡Tu Extracash puede llevarte a México!</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>"👉 Obtén tu Extracash de S/{S} y gana 3,000 Millas sin sorteos. TyC. Hazlo aquí"</t>
+          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>¡Un beneficio pensado para ti!</t>
+          <t>¡Tu Extracash puede llevarte a México!</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>"Con S/{S} estás más cerca de ese viaje o inversión que tanto planeas. Solicítalo hoy "</t>
+          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Pide tu préstamo preaprobado 🚀</t>
+          <t>¡Tu Préstamo puede llevarte a México!</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>"Con S/{S} estás más cerca de ese viaje o inversión que tanto planeas. Solicítalo hoy "</t>
+          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Pide tu préstamo preaprobado 🚀</t>
+          <t>¡Tu Préstamo puede llevarte a México!</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>"Con S/{S} estás más cerca de ese viaje o inversión que tanto planeas. Solicítalo hoy "</t>
+          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Pide tu préstamo preaprobado 🚀</t>
+          <t>¡Tu Préstamo puede llevarte a México!</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>#05BE50</t>
+          <t>#2C675F</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>#0039A6</t>
+          <t>#2C675F</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Prepara las maletas y disfruta tu viaje sin preocupaciones.</t>
+          <t>Disfruta de tu viaje con tranquilidad desde $2 al día.</t>
         </is>
       </c>
       <c r="H150" t="n">
@@ -10552,7 +10552,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/577e06a7-661b-41ce-b69a-cfa538fe5618.png</t>
+          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/92790487-6957-4bae-9f19-2ecae7fa69f6.png</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Incrementa la línea de tu Tarjeta de Crédito hoy a {S} y participa. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC.</t>
+          <t>Aumenta tu línea a S/{S} y entra al sorteo de un iPhone 17 Pro Max. Hazlo aquí hoy. TyC.</t>
         </is>
       </c>
       <c r="H151" t="n">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>"Gana 5,000 Millas ¡sin sorteos!"</t>
+          <t>Tu tarjeta puede darte más</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>"👉 Obtén tu Extracash de S/{S} y gana 3,000 Millas sin sorteos. TyC. Hazlo aquí"</t>
+          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H162" t="n">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>¡Un beneficio pensado para ti!</t>
+          <t>¡Tu Extracash puede llevarte a México!</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>"Con S/{S} estás más cerca de ese viaje o inversión que tanto planeas. Solicítalo hoy "</t>
+          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H163" t="n">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>Pide tu préstamo preaprobado 🚀</t>
+          <t>¡Tu Préstamo puede llevarte a México!</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Prepara las maletas y disfruta tu viaje sin preocupaciones.</t>
+          <t>Disfruta de tu viaje con tranquilidad desde $2 al día.</t>
         </is>
       </c>
       <c r="H198" t="n">
@@ -13788,7 +13788,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/577e06a7-661b-41ce-b69a-cfa538fe5618.png</t>
+          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/92790487-6957-4bae-9f19-2ecae7fa69f6.png</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>"Incremento tu línea hoy "</t>
+          <t>Amplia tu línea de crédito a S/ {S}</t>
         </is>
       </c>
       <c r="H201" t="n">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>Hasta MONTO para ti 😎</t>
+          <t>Incremento de línea</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Pide el 100% de tu Préstamo HOY y entra al sorteo. Serán 5 ganadores. TyC.</t>
+          <t>Con S/{S} estás más cerca de ese viaje o inversión que tanto planeas. Solicítalo hoy.</t>
         </is>
       </c>
       <c r="H225" t="n">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>¡Gana tu Préstamo con 1% TCEA!</t>
+          <t>Pide tu préstamo preaprobado 🚀</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Pide el 100% de tu Préstamo HOY y entra al sorteo. Serán 5 ganadores. TyC.</t>
+          <t>Con S/{S} estás más cerca de ese viaje o inversión que tanto planeas. Solicítalo hoy.</t>
         </is>
       </c>
       <c r="H226" t="n">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>¡Gana tu Préstamo con 1% TCEA!</t>
+          <t>Pide tu préstamo preaprobado 🚀</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Pide el 100% HOY y entra al sorteo de 5 premios. ¡No los dejes pasar! TyC.</t>
+          <t>Con S/{S} estás más cerca de ese viaje o inversión que tanto planeas. Solicítalo hoy.</t>
         </is>
       </c>
       <c r="H227" t="n">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>Tu Préstamo con 1% TCEA</t>
+          <t>Pide tu préstamo preaprobado 🚀</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -34092,7 +34092,7 @@
       <c r="I530" t="inlineStr"/>
       <c r="J530" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/d7feccae-27f3-4c09-b076-5ebd93f29b21.png</t>
+          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/34243619-bd01-458a-b3c6-44cc1639f5a1.png</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
@@ -34327,7 +34327,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>Activa tu Seguro de Viajes 100% online en tu Interbank APP fácil y al instante.</t>
+          <t>Protección completa para tu viaje desde US$2 al día.</t>
         </is>
       </c>
       <c r="H534" t="n">
@@ -34336,7 +34336,7 @@
       <c r="I534" t="inlineStr"/>
       <c r="J534" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/a23dd706-a612-4c93-8f1d-5132a36b2fbd.png</t>
+          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/49a1f70c-d81c-41cb-9ab8-85af452ad38c.png</t>
         </is>
       </c>
       <c r="K534" t="inlineStr">
@@ -34350,7 +34350,7 @@
       </c>
       <c r="N534" t="inlineStr">
         <is>
-          <t>Viaja protegido</t>
+          <t>Seguro de viajes</t>
         </is>
       </c>
       <c r="O534" t="inlineStr">
@@ -35604,7 +35604,7 @@
       <c r="I554" t="inlineStr"/>
       <c r="J554" t="inlineStr">
         <is>
-          <t>"https://content-us-2.content-cms.com/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/dxdam/4f/4f9cacee-b109-422b-8145-c7c1b3f3312f/modulo_banner_rtd_para-ti_tcgl_202604.png "</t>
+          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/b1737867-9a0c-4cda-b7be-b6a3c5ef3a79.png</t>
         </is>
       </c>
       <c r="K554" t="inlineStr">
@@ -35621,7 +35621,11 @@
           <t>La tarjeta perfecta para ti</t>
         </is>
       </c>
-      <c r="O554" t="inlineStr"/>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>https://interbank.pe/solicitar/tarjeta/creditogl/inicio</t>
+        </is>
+      </c>
       <c r="P554" t="n">
         <v>1</v>
       </c>

--- a/data/resultado.xlsx
+++ b/data/resultado.xlsx
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SEGURO VIVE SAULD</t>
+          <t>SEGURO VIVE SALUD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SEGURO VIVE SALUD +</t>
+          <t>SEGURO VIVE SALUD</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6472,8 +6472,16 @@
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AUDIENCIA RENTA ALTA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SEGURO VIAJES</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>1-1J52163J#AU1#0#1</t>
@@ -10403,7 +10411,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SEGURO VIVE SALUD +</t>
+          <t>SEGURO VIVE SALUD</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -10524,8 +10532,16 @@
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>AUDIENCIA RENTA ALTA SELECT</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SEGURO VIAJES</t>
+        </is>
+      </c>
       <c r="D150" t="inlineStr">
         <is>
           <t>1-1J52163J#AU2#0#1</t>
@@ -13639,7 +13655,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SEGURO VIVE SALUD +</t>
+          <t>SEGURO VIVE SALUD</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -13760,8 +13776,16 @@
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
-      <c r="B198" t="inlineStr"/>
-      <c r="C198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>AUDIENCIA DEFAULT</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SEGURO VIAJES</t>
+        </is>
+      </c>
       <c r="D198" t="inlineStr">
         <is>
           <t>1-1J52163J#AUD#0#1</t>
@@ -16944,8 +16968,16 @@
     </row>
     <row r="245">
       <c r="A245" t="inlineStr"/>
-      <c r="B245" t="inlineStr"/>
-      <c r="C245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>AUDIENCIA DEFAULT</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>TARJETA DE CREDITO GL</t>
+        </is>
+      </c>
       <c r="D245" t="inlineStr">
         <is>
           <t>1-K1WWS0N#AUD#0</t>
@@ -19236,8 +19268,16 @@
     </row>
     <row r="279">
       <c r="A279" t="inlineStr"/>
-      <c r="B279" t="inlineStr"/>
-      <c r="C279" t="inlineStr"/>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>CAPA DE MEMORIA</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>TARJETA DE CREDITO GL</t>
+        </is>
+      </c>
       <c r="D279" t="inlineStr">
         <is>
           <t>1-K1WWS0N#CAP#0</t>
@@ -20455,7 +20495,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>SEGURO VIVE SALUD +</t>
+          <t>SEGURO VIVE SALUD</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -23967,21 +24007,9 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - ECOM - IL</t>
-        </is>
-      </c>
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" t="inlineStr"/>
+      <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
           <t>1-1JHP8B#51#TC#ECOM#2#PUSH#1</t>
@@ -24023,21 +24051,9 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
           <t>1-1JHP8B#51#TC#ECOM#2#UNI#SMS#1</t>
@@ -24083,21 +24099,9 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - ECOM - IL</t>
-        </is>
-      </c>
+      <c r="A351" t="inlineStr"/>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
           <t>1-1JHP8B#51#TD#ECOM#2#PUSH#1</t>
@@ -24139,21 +24143,9 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A352" t="inlineStr"/>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
           <t>1-1JHP8B#51#TD#ECOM#2#UNI#SMS#1</t>
@@ -24199,21 +24191,9 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - ECOM - ADS</t>
-        </is>
-      </c>
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
           <t>1-2QIP2#51#TD#ECOM#2#PUSH#1</t>
@@ -24255,21 +24235,9 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - ECOM - ADS</t>
-        </is>
-      </c>
+      <c r="A354" t="inlineStr"/>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
           <t>1-2QIP2#51#TD#ECOM#2#UNI#SMS#1</t>
@@ -24315,21 +24283,9 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - ECOM - ALCANCIA</t>
-        </is>
-      </c>
+      <c r="A355" t="inlineStr"/>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
           <t>ALC#51#TD#ECOM#2#PUSH#1</t>
@@ -24371,21 +24327,9 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - ECOM - ALCANCIA</t>
-        </is>
-      </c>
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
           <t>ALC#51#TD#ECOM#2#UNI#SMS#1</t>
@@ -24431,21 +24375,9 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A357" t="inlineStr"/>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
           <t>DNG#14#TC#ECOM#2#UNI#SMS#1</t>
@@ -24491,21 +24423,9 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A358" t="inlineStr"/>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
           <t>DNG#14#TD#ECOM#2#UNI#SMS#1</t>
@@ -24551,21 +24471,9 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
           <t>DNG#41#TC#ECOM#2#UNI#SMS#1</t>
@@ -24611,21 +24519,9 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
           <t>DNG#41#TD#ECOM#2#UNI#SMS#1</t>
@@ -24671,21 +24567,9 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A361" t="inlineStr"/>
+      <c r="B361" t="inlineStr"/>
+      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
           <t>DNG#43#TC#ECOM#2#UNI#SMS#1</t>
@@ -24731,21 +24615,9 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
           <t>DNG#43#TD#ECOM#2#UNI#SMS#1</t>
@@ -24791,21 +24663,9 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - ECOM</t>
-        </is>
-      </c>
+      <c r="A363" t="inlineStr"/>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
           <t>DNG#51#TC#ECOM#2#UNI#SMS#1</t>
@@ -24851,21 +24711,9 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - ECOM</t>
-        </is>
-      </c>
+      <c r="A364" t="inlineStr"/>
+      <c r="B364" t="inlineStr"/>
+      <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
           <t>DNG#51#TD#ECOM#2#UNI#SMS#1</t>
@@ -24911,21 +24759,9 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A365" t="inlineStr"/>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
           <t>DNG#52#TC#ECOM#2#UNI#SMS#1</t>
@@ -24971,21 +24807,9 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A366" t="inlineStr"/>
+      <c r="B366" t="inlineStr"/>
+      <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
           <t>DNG#52#TD#ECOM#2#UNI#SMS#1</t>
@@ -25031,21 +24855,9 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A367" t="inlineStr"/>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
           <t>DNG#54#TC#ECOM#2#UNI#SMS#1</t>
@@ -25091,21 +24903,9 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A368" t="inlineStr"/>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
           <t>DNG#54#TD#ECOM#2#UNI#SMS#1</t>
@@ -25343,21 +25143,9 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>PRENDE/APAGA  TC - ECOM</t>
-        </is>
-      </c>
+      <c r="A373" t="inlineStr"/>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
           <t>DNG#57#TC#ECOM#2#PUSH#1</t>
@@ -25399,21 +25187,9 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>PRENDE/APAGA  TC - ECOM</t>
-        </is>
-      </c>
+      <c r="A374" t="inlineStr"/>
+      <c r="B374" t="inlineStr"/>
+      <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
           <t>DNG#57#TC#ECOM#2#UNI#SMS#1</t>
@@ -25459,21 +25235,9 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>PRENDE/APAGA  TC - ECOM</t>
-        </is>
-      </c>
+      <c r="A375" t="inlineStr"/>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
           <t>DNG#57#TD#ECOM#2#UNI#SMS#1</t>
@@ -25519,21 +25283,9 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A376" t="inlineStr"/>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
           <t>DNG#62#TC#ECOM#2#UNI#SMS#1</t>
@@ -25575,21 +25327,9 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A377" t="inlineStr"/>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
           <t>DNG#62#TD#ECOM#2#UNI#SMS#1</t>
@@ -25631,21 +25371,9 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A378" t="inlineStr"/>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
           <t>DNG#69#TC#ECOM#2#UNI#SMS#1</t>
@@ -25691,21 +25419,9 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A379" t="inlineStr"/>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
           <t>DNG#69#TD#ECOM#2#UNI#SMS#1</t>
@@ -25847,21 +25563,9 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>ERROR CVV TC - ECOM</t>
-        </is>
-      </c>
+      <c r="A382" t="inlineStr"/>
+      <c r="B382" t="inlineStr"/>
+      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
           <t>DNG#N7#TC#ECOM#2#PUSH#1</t>
@@ -25903,21 +25607,9 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>ERROR CVV TC - ECOM</t>
-        </is>
-      </c>
+      <c r="A383" t="inlineStr"/>
+      <c r="B383" t="inlineStr"/>
+      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
           <t>DNG#N7#TC#ECOM#2#UNI#SMS#1</t>
@@ -25963,21 +25655,9 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>ERROR CVV TD - ECOM</t>
-        </is>
-      </c>
+      <c r="A384" t="inlineStr"/>
+      <c r="B384" t="inlineStr"/>
+      <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
           <t>DNG#N7#TD#ECOM#2#PUSH#1</t>
@@ -26019,21 +25699,9 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>ERROR CVV TD - ECOM</t>
-        </is>
-      </c>
+      <c r="A385" t="inlineStr"/>
+      <c r="B385" t="inlineStr"/>
+      <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
           <t>DNG#N7#TD#ECOM#2#UNI#SMS#1</t>
@@ -26079,21 +25747,9 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A386" t="inlineStr"/>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
           <t>DNG#SD#TC#ECOM#2#UNI#SMS#1</t>
@@ -26139,21 +25795,9 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A387" t="inlineStr"/>
+      <c r="B387" t="inlineStr"/>
+      <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
           <t>DNG#SD#TD#ECOM#2#UNI#SMS#1</t>
@@ -26199,21 +25843,9 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>MORA TEMPORAL TC - ECOM</t>
-        </is>
-      </c>
+      <c r="A388" t="inlineStr"/>
+      <c r="B388" t="inlineStr"/>
+      <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
           <t>DNG#T4#TC#ECOM#2#PUSH#1</t>
@@ -26255,21 +25887,9 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>MORA TEMPORAL TC - ECOM</t>
-        </is>
-      </c>
+      <c r="A389" t="inlineStr"/>
+      <c r="B389" t="inlineStr"/>
+      <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
           <t>DNG#T4#TC#ECOM#2#UNI#SMS#1</t>
@@ -26315,21 +25935,9 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>MORA TEMPORAL TD - ECOM</t>
-        </is>
-      </c>
+      <c r="A390" t="inlineStr"/>
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
           <t>DNG#T4#TD#ECOM#2#UNI#SMS#1</t>
@@ -26375,21 +25983,9 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>COMPRAS ONLINE TC - ECOM</t>
-        </is>
-      </c>
+      <c r="A391" t="inlineStr"/>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
           <t>DNG#T6#TC#ECOM#2#PUSH#1</t>
@@ -26431,21 +26027,9 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>COMPRAS ONLINE TC - ECOM</t>
-        </is>
-      </c>
+      <c r="A392" t="inlineStr"/>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
           <t>DNG#T6#TC#ECOM#2#UNI#SMS#1</t>
@@ -26491,21 +26075,9 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>COMPRAS ONLINE TCA - ECOM</t>
-        </is>
-      </c>
+      <c r="A393" t="inlineStr"/>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
           <t>DNG#T6#TC#TA#ECOM#2#PUSH#1</t>
@@ -26547,21 +26119,9 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>COMPRAS ONLINE TCA - ECOM</t>
-        </is>
-      </c>
+      <c r="A394" t="inlineStr"/>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
           <t>DNG#T6#TC#TA#ECOM#2#UNI#SMS#1</t>
@@ -26603,21 +26163,9 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>COMPRAS ONLINE TD - ECOM</t>
-        </is>
-      </c>
+      <c r="A395" t="inlineStr"/>
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
           <t>DNG#T6#TD#ECOM#2#PUSH#1</t>
@@ -26659,21 +26207,9 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>COMPRAS ONLINE TD - ECOM</t>
-        </is>
-      </c>
+      <c r="A396" t="inlineStr"/>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
           <t>DNG#T6#TD#ECOM#2#UNI#SMS#1</t>
@@ -26719,21 +26255,9 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>SOBREGIRO TC - ECOM</t>
-        </is>
-      </c>
+      <c r="A397" t="inlineStr"/>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
           <t>DNG#Z6#TC#ECOM#2#PUSH#1</t>
@@ -26775,21 +26299,9 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>SOBREGIRO TC - ECOM</t>
-        </is>
-      </c>
+      <c r="A398" t="inlineStr"/>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
           <t>DNG#Z6#TC#ECOM#2#UNI#SMS#1</t>
@@ -26883,21 +26395,9 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - POS</t>
-        </is>
-      </c>
+      <c r="A400" t="inlineStr"/>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
           <t>TC#51#TD#ECOM#2#UNI#SMS#1</t>
@@ -26939,21 +26439,9 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - POS - TCA</t>
-        </is>
-      </c>
+      <c r="A401" t="inlineStr"/>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
           <t>TCA#51#TC#ECOM#2#UNI#SMS#1</t>
@@ -26995,21 +26483,9 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - ECOM</t>
-        </is>
-      </c>
+      <c r="A402" t="inlineStr"/>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
           <t>UC#51#TC#ECOM#2#PUSH#1</t>
@@ -27051,21 +26527,9 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - ECOM</t>
-        </is>
-      </c>
+      <c r="A403" t="inlineStr"/>
+      <c r="B403" t="inlineStr"/>
+      <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
           <t>UC#51#TC#ECOM#2#UNI#SMS#1</t>
@@ -27111,21 +26575,9 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - POS - IL</t>
-        </is>
-      </c>
+      <c r="A404" t="inlineStr"/>
+      <c r="B404" t="inlineStr"/>
+      <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
           <t>1-1JHP8B#51#TC#POS#2#PUSH#1</t>
@@ -27167,21 +26619,9 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A405" t="inlineStr"/>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
           <t>1-1JHP8B#51#TC#POS#2#UNI#SMS#1</t>
@@ -27227,21 +26667,9 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - POS - IL</t>
-        </is>
-      </c>
+      <c r="A406" t="inlineStr"/>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
           <t>1-1JHP8B#51#TD#POS#2#PUSH#1</t>
@@ -27283,21 +26711,9 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A407" t="inlineStr"/>
+      <c r="B407" t="inlineStr"/>
+      <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
           <t>1-1JHP8B#51#TD#POS#2#UNI#SMS#1</t>
@@ -27343,21 +26759,9 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - POS - ADS</t>
-        </is>
-      </c>
+      <c r="A408" t="inlineStr"/>
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
           <t>1-2QIP2#51#TD#POS#2#PUSH#1</t>
@@ -27399,21 +26803,9 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - POS - ADS</t>
-        </is>
-      </c>
+      <c r="A409" t="inlineStr"/>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
           <t>1-2QIP2#51#TD#POS#2#UNI#SMS#1</t>
@@ -27459,21 +26851,9 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - POS - ALCANCIA</t>
-        </is>
-      </c>
+      <c r="A410" t="inlineStr"/>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
           <t>ALC#51#TD#POS#2#PUSH#1</t>
@@ -27515,21 +26895,9 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - POS - ALCANCIA</t>
-        </is>
-      </c>
+      <c r="A411" t="inlineStr"/>
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
           <t>ALC#51#TD#POS#2#UNI#SMS#1</t>
@@ -27575,21 +26943,9 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>ERROR PIN TC - POS</t>
-        </is>
-      </c>
+      <c r="A412" t="inlineStr"/>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
           <t>CP#55#TC#POS#2#PUSH#1</t>
@@ -27631,21 +26987,9 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>ERROR PIN TC - POS</t>
-        </is>
-      </c>
+      <c r="A413" t="inlineStr"/>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
           <t>CP#55#TC#POS#2#UNI#SMS#1</t>
@@ -27691,21 +27035,9 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A414" t="inlineStr"/>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
           <t>DNG#14#TC#POS#2#UNI#SMS#1</t>
@@ -27751,21 +27083,9 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A415" t="inlineStr"/>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
           <t>DNG#14#TD#POS#2#UNI#SMS#1</t>
@@ -27811,21 +27131,9 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A416" t="inlineStr"/>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
           <t>DNG#41#TC#POS#2#UNI#SMS#1</t>
@@ -27871,21 +27179,9 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A417" t="inlineStr"/>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
           <t>DNG#41#TD#POS#2#UNI#SMS#1</t>
@@ -27931,21 +27227,9 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A418" t="inlineStr"/>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
           <t>DNG#43#TC#POS#2#UNI#SMS#1</t>
@@ -27991,21 +27275,9 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A419" t="inlineStr"/>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
           <t>DNG#43#TD#POS#2#UNI#SMS#1</t>
@@ -28051,21 +27323,9 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - POS</t>
-        </is>
-      </c>
+      <c r="A420" t="inlineStr"/>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
           <t>DNG#51#TC#POS#2#UNI#SMS#1</t>
@@ -28111,21 +27371,9 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - POS</t>
-        </is>
-      </c>
+      <c r="A421" t="inlineStr"/>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
           <t>DNG#51#TD#POS#2#UNI#SMS#1</t>
@@ -28171,21 +27419,9 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A422" t="inlineStr"/>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
           <t>DNG#52#TC#POS#2#UNI#SMS#1</t>
@@ -28231,21 +27467,9 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A423" t="inlineStr"/>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
           <t>DNG#52#TD#POS#2#UNI#SMS#1</t>
@@ -28291,21 +27515,9 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A424" t="inlineStr"/>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
           <t>DNG#54#TC#POS#2#UNI#SMS#1</t>
@@ -28351,21 +27563,9 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A425" t="inlineStr"/>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
           <t>DNG#54#TD#POS#2#UNI#SMS#1</t>
@@ -28603,21 +27803,9 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>PRENDE/APAGA  TC - POS</t>
-        </is>
-      </c>
+      <c r="A430" t="inlineStr"/>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
           <t>DNG#57#TC#POS#2#PUSH#1</t>
@@ -28659,21 +27847,9 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>PRENDE/APAGA  TC - POS</t>
-        </is>
-      </c>
+      <c r="A431" t="inlineStr"/>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
           <t>DNG#57#TC#POS#2#UNI#SMS#1</t>
@@ -28719,21 +27895,9 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>PRENDE/APAGA  TC - POS</t>
-        </is>
-      </c>
+      <c r="A432" t="inlineStr"/>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
           <t>DNG#57#TD#POS#2#UNI#SMS#1</t>
@@ -28779,21 +27943,9 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A433" t="inlineStr"/>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
           <t>DNG#62#TC#POS#2#UNI#SMS#1</t>
@@ -28835,21 +27987,9 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A434" t="inlineStr"/>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
           <t>DNG#62#TD#POS#2#UNI#SMS#1</t>
@@ -28891,21 +28031,9 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A435" t="inlineStr"/>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
           <t>DNG#69#TC#POS#2#UNI#SMS#1</t>
@@ -28951,21 +28079,9 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A436" t="inlineStr"/>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
           <t>DNG#69#TD#POS#2#UNI#SMS#1</t>
@@ -29203,21 +28319,9 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A441" t="inlineStr"/>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
           <t>DNG#SD#TC#POS#2#UNI#SMS#1</t>
@@ -29263,21 +28367,9 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A442" t="inlineStr"/>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
           <t>DNG#SD#TD#POS#2#UNI#SMS#1</t>
@@ -29323,21 +28415,9 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>MORA TEMPORAL TC - POS</t>
-        </is>
-      </c>
+      <c r="A443" t="inlineStr"/>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
           <t>DNG#T4#TC#POS#2#PUSH#1</t>
@@ -29379,21 +28459,9 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>MORA TEMPORAL TC - POS</t>
-        </is>
-      </c>
+      <c r="A444" t="inlineStr"/>
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
           <t>DNG#T4#TC#POS#2#UNI#SMS#1</t>
@@ -29439,21 +28507,9 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>MORA TEMPORAL TD - POS</t>
-        </is>
-      </c>
+      <c r="A445" t="inlineStr"/>
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
           <t>DNG#T4#TD#POS#2#UNI#SMS#1</t>
@@ -29595,21 +28651,9 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>SOBREGIRO TC - POS</t>
-        </is>
-      </c>
+      <c r="A448" t="inlineStr"/>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
           <t>DNG#Z6#TC#POS#2#PUSH#1</t>
@@ -29651,21 +28695,9 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>SOBREGIRO TC - POS</t>
-        </is>
-      </c>
+      <c r="A449" t="inlineStr"/>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
           <t>DNG#Z6#TC#POS#2#UNI#SMS#1</t>
@@ -29759,21 +28791,9 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>NO CAMBIO PIN TC - POS</t>
-        </is>
-      </c>
+      <c r="A451" t="inlineStr"/>
+      <c r="B451" t="inlineStr"/>
+      <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
           <t>SP#55#TC#POS#2#PUSH#1</t>
@@ -29815,21 +28835,9 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>NO CAMBIO PIN TC - POS</t>
-        </is>
-      </c>
+      <c r="A452" t="inlineStr"/>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
           <t>SP#55#TC#POS#2#UNI#SMS#1</t>
@@ -29871,21 +28879,9 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - POS</t>
-        </is>
-      </c>
+      <c r="A453" t="inlineStr"/>
+      <c r="B453" t="inlineStr"/>
+      <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
           <t>TC#51#TD#POS#2#UNI#SMS#1</t>
@@ -29927,21 +28923,9 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - POS - TCA</t>
-        </is>
-      </c>
+      <c r="A454" t="inlineStr"/>
+      <c r="B454" t="inlineStr"/>
+      <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
           <t>TCA#51#TC#POS#2#UNI#SMS#1</t>
@@ -29983,21 +28967,9 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - POS</t>
-        </is>
-      </c>
+      <c r="A455" t="inlineStr"/>
+      <c r="B455" t="inlineStr"/>
+      <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
           <t>UC#51#TC#POS#2#PUSH#1</t>
@@ -30039,21 +29011,9 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - POS</t>
-        </is>
-      </c>
+      <c r="A456" t="inlineStr"/>
+      <c r="B456" t="inlineStr"/>
+      <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
           <t>UC#51#TC#POS#2#UNI#SMS#1</t>
@@ -30099,21 +29059,9 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - RECUR - ALCANCIA</t>
-        </is>
-      </c>
+      <c r="A457" t="inlineStr"/>
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
           <t>ALC#51#TD#RECUR#2#PUSH#1</t>
@@ -30155,21 +29103,9 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - RECUR - ALCANCIA</t>
-        </is>
-      </c>
+      <c r="A458" t="inlineStr"/>
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr">
         <is>
           <t>ALC#51#TD#RECUR#2#UNI#SMS#1</t>
@@ -30215,21 +29151,9 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A459" t="inlineStr"/>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr">
         <is>
           <t>DNG#14#TC#RECUR#2#UNI#SMS#1</t>
@@ -30271,21 +29195,9 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A460" t="inlineStr"/>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr">
         <is>
           <t>DNG#14#TD#RECUR#2#UNI#SMS#1</t>
@@ -30327,21 +29239,9 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A461" t="inlineStr"/>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr">
         <is>
           <t>DNG#41#TC#RECUR#2#UNI#SMS#1</t>
@@ -30383,21 +29283,9 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A462" t="inlineStr"/>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr">
         <is>
           <t>DNG#41#TD#RECUR#2#UNI#SMS#1</t>
@@ -30439,21 +29327,9 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A463" t="inlineStr"/>
+      <c r="B463" t="inlineStr"/>
+      <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr">
         <is>
           <t>DNG#43#TC#RECUR#2#UNI#SMS#1</t>
@@ -30495,21 +29371,9 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A464" t="inlineStr"/>
+      <c r="B464" t="inlineStr"/>
+      <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr">
         <is>
           <t>DNG#43#TD#RECUR#2#UNI#SMS#1</t>
@@ -30551,21 +29415,9 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - RECUR</t>
-        </is>
-      </c>
+      <c r="A465" t="inlineStr"/>
+      <c r="B465" t="inlineStr"/>
+      <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr">
         <is>
           <t>DNG#51#TC#RECUR#2#UNI#SMS#1</t>
@@ -30611,21 +29463,9 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>SALDO INSUFICIENTE - RECUR</t>
-        </is>
-      </c>
+      <c r="A466" t="inlineStr"/>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr">
         <is>
           <t>DNG#51#TD#RECUR#2#UNI#SMS#1</t>
@@ -30667,21 +29507,9 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A467" t="inlineStr"/>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" t="inlineStr"/>
       <c r="D467" t="inlineStr">
         <is>
           <t>DNG#52#TC#RECUR#2#UNI#SMS#1</t>
@@ -30723,21 +29551,9 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A468" t="inlineStr"/>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr"/>
       <c r="D468" t="inlineStr">
         <is>
           <t>DNG#52#TD#RECUR#2#UNI#SMS#1</t>
@@ -30779,21 +29595,9 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A469" t="inlineStr"/>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
           <t>DNG#54#TC#RECUR#2#UNI#SMS#1</t>
@@ -30835,21 +29639,9 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A470" t="inlineStr"/>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
         <is>
           <t>DNG#54#TD#RECUR#2#UNI#SMS#1</t>
@@ -30891,21 +29683,9 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>PRENDE/APAGA  TC - RECUR</t>
-        </is>
-      </c>
+      <c r="A471" t="inlineStr"/>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
           <t>DNG#57#TC#RECUR#2#PUSH#1</t>
@@ -30947,21 +29727,9 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A472" t="inlineStr"/>
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
           <t>DNG#62#TC#RECUR#2#UNI#SMS#1</t>
@@ -31003,21 +29771,9 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A473" t="inlineStr"/>
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
           <t>DNG#62#TD#RECUR#2#UNI#SMS#1</t>
@@ -31059,21 +29815,9 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A474" t="inlineStr"/>
+      <c r="B474" t="inlineStr"/>
+      <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
           <t>DNG#69#TC#RECUR#2#UNI#SMS#1</t>
@@ -31115,21 +29859,9 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A475" t="inlineStr"/>
+      <c r="B475" t="inlineStr"/>
+      <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
           <t>DNG#69#TD#RECUR#2#UNI#SMS#1</t>
@@ -31171,21 +29903,9 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A476" t="inlineStr"/>
+      <c r="B476" t="inlineStr"/>
+      <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
           <t>DNG#SD#TC#RECUR#2#UNI#SMS#1</t>
@@ -31227,21 +29947,9 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A477" t="inlineStr"/>
+      <c r="B477" t="inlineStr"/>
+      <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
           <t>DNG#SD#TD#RECUR#2#UNI#SMS#1</t>
@@ -31283,21 +29991,9 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>MORA TEMPORAL TC - RECUR</t>
-        </is>
-      </c>
+      <c r="A478" t="inlineStr"/>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
           <t>DNG#T4#TC#RECUR#2#PUSH#1</t>
@@ -31339,21 +30035,9 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - RECUR</t>
-        </is>
-      </c>
+      <c r="A479" t="inlineStr"/>
+      <c r="B479" t="inlineStr"/>
+      <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
           <t>UC#51#TC#RECUR#2#PUSH#1</t>
@@ -31395,21 +30079,9 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>EXCEDE LINEA DE CREDITO - RECUR</t>
-        </is>
-      </c>
+      <c r="A480" t="inlineStr"/>
+      <c r="B480" t="inlineStr"/>
+      <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
           <t>UC#51#TC#RECUR#2#UNI#SMS#1</t>
@@ -31455,21 +30127,9 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>DEPÓSITO EN TIENDA</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>FIRST</t>
-        </is>
-      </c>
+      <c r="A481" t="inlineStr"/>
+      <c r="B481" t="inlineStr"/>
+      <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
           <t>DEPOSITO_F#TDA#3#1</t>
@@ -31507,21 +30167,9 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>DEPÓSITO EN TIENDA</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
+      <c r="A482" t="inlineStr"/>
+      <c r="B482" t="inlineStr"/>
+      <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
           <t>DEPOSITO_L#TDA#3#1</t>
@@ -31559,21 +30207,9 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>DEPÓSITO EN TIENDA</t>
-        </is>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A483" t="inlineStr"/>
+      <c r="B483" t="inlineStr"/>
+      <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr">
         <is>
           <t>DEPOSITO_L#TDA#3#2</t>
@@ -31611,21 +30247,9 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A484" t="inlineStr"/>
+      <c r="B484" t="inlineStr"/>
+      <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr">
         <is>
           <t>RETIRO_F#TDA#3#1</t>
@@ -31663,21 +30287,9 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>RETIRO EN TIENDA</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
+      <c r="A485" t="inlineStr"/>
+      <c r="B485" t="inlineStr"/>
+      <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr">
         <is>
           <t>RETIRO_L#TDA#3#1</t>
@@ -31715,21 +30327,9 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>SUPERMERCADOS</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>SUPERMERCADOS</t>
-        </is>
-      </c>
+      <c r="A486" t="inlineStr"/>
+      <c r="B486" t="inlineStr"/>
+      <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr">
         <is>
           <t>SUPERMERCADO#TD#POS#4#1</t>
@@ -31767,21 +30367,9 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
+      <c r="A487" t="inlineStr"/>
+      <c r="B487" t="inlineStr"/>
+      <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr">
         <is>
           <t>1-2QIP2#ECOM#5#PUSH#1</t>
@@ -31823,21 +30411,9 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
+      <c r="A488" t="inlineStr"/>
+      <c r="B488" t="inlineStr"/>
+      <c r="C488" t="inlineStr"/>
       <c r="D488" t="inlineStr">
         <is>
           <t>1-2QIP2#ECOM#5#SMS#1</t>
@@ -31879,21 +30455,9 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
+      <c r="A489" t="inlineStr"/>
+      <c r="B489" t="inlineStr"/>
+      <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr">
         <is>
           <t>1-2QIP2#POS#5#PUSH#1</t>
@@ -31935,21 +30499,9 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
+      <c r="A490" t="inlineStr"/>
+      <c r="B490" t="inlineStr"/>
+      <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr">
         <is>
           <t>1-2QIP2#POS#5#SMS#1</t>
@@ -31991,21 +30543,9 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>CONSUMO ATÍPICO</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A491" t="inlineStr"/>
+      <c r="B491" t="inlineStr"/>
+      <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr">
         <is>
           <t>1-1JHP8B#ATY#ECOM#6#1</t>
@@ -32043,21 +30583,9 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>CONSUMO ATÍPICO</t>
-        </is>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A492" t="inlineStr"/>
+      <c r="B492" t="inlineStr"/>
+      <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr">
         <is>
           <t>1-1JHP8B#ATY#ECOM#6#PUSH#1</t>
@@ -32095,21 +30623,9 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>CONSUMO ATÍPICO</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A493" t="inlineStr"/>
+      <c r="B493" t="inlineStr"/>
+      <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr">
         <is>
           <t>1-1JHP8B#ATY#ECOM#6#SMS#1</t>
@@ -32147,21 +30663,9 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A494" t="inlineStr"/>
+      <c r="B494" t="inlineStr"/>
+      <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr">
         <is>
           <t>1-1JHP8B#CLT#ECOM#6#1</t>
@@ -32199,21 +30703,9 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A495" t="inlineStr"/>
+      <c r="B495" t="inlineStr"/>
+      <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr">
         <is>
           <t>1-1JHP8B#CLT#ECOM#6#2</t>
@@ -32251,21 +30743,9 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A496" t="inlineStr"/>
+      <c r="B496" t="inlineStr"/>
+      <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr">
         <is>
           <t>1-1JHP8B#CLT#ECOM#6#PUSH#1</t>
@@ -32303,21 +30783,9 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A497" t="inlineStr"/>
+      <c r="B497" t="inlineStr"/>
+      <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr">
         <is>
           <t>1-1JHP8B#CLT#ECOM#6#SMS#1</t>
@@ -32355,21 +30823,9 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>CONSUMO ATÍPICO</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A498" t="inlineStr"/>
+      <c r="B498" t="inlineStr"/>
+      <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr">
         <is>
           <t>1-8R42A#ATY#ECOM#6#1</t>
@@ -32407,21 +30863,9 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A499" t="inlineStr"/>
+      <c r="B499" t="inlineStr"/>
+      <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
           <t>1-8R42A#ATY#ECOM#6#PUSH#1</t>
@@ -32459,21 +30903,9 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>CONSUMO ATÍPICO</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A500" t="inlineStr"/>
+      <c r="B500" t="inlineStr"/>
+      <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
           <t>1-8R42A#ATY#ECOM#6#SMS#1</t>
@@ -32511,21 +30943,9 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A501" t="inlineStr"/>
+      <c r="B501" t="inlineStr"/>
+      <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
           <t>1-8R42A#CLT#ECOM#6#1</t>
@@ -32563,21 +30983,9 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A502" t="inlineStr"/>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
           <t>1-8R42A#CLT#ECOM#6#2</t>
@@ -32615,21 +31023,9 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A503" t="inlineStr"/>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
           <t>1-8R42A#CLT#ECOM#6#PUSH#1</t>
@@ -32667,21 +31063,9 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A504" t="inlineStr"/>
+      <c r="B504" t="inlineStr"/>
+      <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
           <t>1-8R42A#CLT#ECOM#6#SMS#1</t>
@@ -32719,21 +31103,9 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>CONSUMO ATÍPICO</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A505" t="inlineStr"/>
+      <c r="B505" t="inlineStr"/>
+      <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
           <t>1-1JHP8B#ATY#POS#6#1</t>
@@ -32771,21 +31143,9 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A506" t="inlineStr"/>
+      <c r="B506" t="inlineStr"/>
+      <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr">
         <is>
           <t>1-1JHP8B#ATY#POS#6#PUSH#1</t>
@@ -32823,21 +31183,9 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>CONSUMO ATÍPICO</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A507" t="inlineStr"/>
+      <c r="B507" t="inlineStr"/>
+      <c r="C507" t="inlineStr"/>
       <c r="D507" t="inlineStr">
         <is>
           <t>1-1JHP8B#ATY#POS#6#SMS#1</t>
@@ -32875,21 +31223,9 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A508" t="inlineStr"/>
+      <c r="B508" t="inlineStr"/>
+      <c r="C508" t="inlineStr"/>
       <c r="D508" t="inlineStr">
         <is>
           <t>1-1JHP8B#CLT#POS#6#1</t>
@@ -32927,21 +31263,9 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A509" t="inlineStr"/>
+      <c r="B509" t="inlineStr"/>
+      <c r="C509" t="inlineStr"/>
       <c r="D509" t="inlineStr">
         <is>
           <t>1-1JHP8B#CLT#POS#6#2</t>
@@ -32979,21 +31303,9 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A510" t="inlineStr"/>
+      <c r="B510" t="inlineStr"/>
+      <c r="C510" t="inlineStr"/>
       <c r="D510" t="inlineStr">
         <is>
           <t>1-1JHP8B#CLT#POS#6#PUSH#1</t>
@@ -33031,21 +31343,9 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A511" t="inlineStr"/>
+      <c r="B511" t="inlineStr"/>
+      <c r="C511" t="inlineStr"/>
       <c r="D511" t="inlineStr">
         <is>
           <t>1-1JHP8B#CLT#POS#6#SMS#1</t>
@@ -33083,21 +31383,9 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A512" t="inlineStr"/>
+      <c r="B512" t="inlineStr"/>
+      <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr">
         <is>
           <t>1-8R42A#ATY#POS#6#1</t>
@@ -33135,21 +31423,9 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A513" t="inlineStr"/>
+      <c r="B513" t="inlineStr"/>
+      <c r="C513" t="inlineStr"/>
       <c r="D513" t="inlineStr">
         <is>
           <t>1-8R42A#ATY#POS#6#PUSH#1</t>
@@ -33187,21 +31463,9 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>CONSUMO ATÍPICO</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A514" t="inlineStr"/>
+      <c r="B514" t="inlineStr"/>
+      <c r="C514" t="inlineStr"/>
       <c r="D514" t="inlineStr">
         <is>
           <t>1-8R42A#ATY#POS#6#SMS#1</t>
@@ -33239,21 +31503,9 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A515" t="inlineStr"/>
+      <c r="B515" t="inlineStr"/>
+      <c r="C515" t="inlineStr"/>
       <c r="D515" t="inlineStr">
         <is>
           <t>1-8R42A#CLT#POS#6#1</t>
@@ -33291,21 +31543,9 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A516" t="inlineStr"/>
+      <c r="B516" t="inlineStr"/>
+      <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr">
         <is>
           <t>1-8R42A#CLT#POS#6#PUSH#1</t>
@@ -33343,21 +31583,9 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A517" t="inlineStr"/>
+      <c r="B517" t="inlineStr"/>
+      <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr">
         <is>
           <t>1-8R42A#CLT#POS#6#SMS#1</t>
@@ -33395,21 +31623,9 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>RETIRO ATM</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A518" t="inlineStr"/>
+      <c r="B518" t="inlineStr"/>
+      <c r="C518" t="inlineStr"/>
       <c r="D518" t="inlineStr">
         <is>
           <t>1-1JHP8B#ATM#7#1</t>
@@ -33451,21 +31667,9 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>RETIRO ATM</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A519" t="inlineStr"/>
+      <c r="B519" t="inlineStr"/>
+      <c r="C519" t="inlineStr"/>
       <c r="D519" t="inlineStr">
         <is>
           <t>1-1JHP8B#ATM#7#2</t>
@@ -33507,21 +31711,9 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>RETIRO ATM</t>
-        </is>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
+      <c r="A520" t="inlineStr"/>
+      <c r="B520" t="inlineStr"/>
+      <c r="C520" t="inlineStr"/>
       <c r="D520" t="inlineStr">
         <is>
           <t>1-2QIP2#ATM#7#1</t>
@@ -33559,21 +31751,9 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>RETIRO ATM</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>SEGURO 360</t>
-        </is>
-      </c>
+      <c r="A521" t="inlineStr"/>
+      <c r="B521" t="inlineStr"/>
+      <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr">
         <is>
           <t>1-3FGE7FL#ATM#7#1</t>
@@ -33611,21 +31791,9 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>RETIRO ATM</t>
-        </is>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>SEGURO FIT</t>
-        </is>
-      </c>
+      <c r="A522" t="inlineStr"/>
+      <c r="B522" t="inlineStr"/>
+      <c r="C522" t="inlineStr"/>
       <c r="D522" t="inlineStr">
         <is>
           <t>1-AKYCZ42#ATM#7#1</t>
@@ -33663,21 +31831,9 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>BANNER ATM</t>
-        </is>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A523" t="inlineStr"/>
+      <c r="B523" t="inlineStr"/>
+      <c r="C523" t="inlineStr"/>
       <c r="D523" t="inlineStr">
         <is>
           <t>1-1JHP8B#ATM#8#1</t>
@@ -33723,21 +31879,9 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>BANNER ATM</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>CONSENTIMIENTO DE DATOS</t>
-        </is>
-      </c>
+      <c r="A524" t="inlineStr"/>
+      <c r="B524" t="inlineStr"/>
+      <c r="C524" t="inlineStr"/>
       <c r="D524" t="inlineStr">
         <is>
           <t>1-5ABM35G#ATM#8#1</t>
@@ -33783,21 +31927,9 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>RETIRO EN AGENTES</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>EDUCACIÓN</t>
-        </is>
-      </c>
+      <c r="A525" t="inlineStr"/>
+      <c r="B525" t="inlineStr"/>
+      <c r="C525" t="inlineStr"/>
       <c r="D525" t="inlineStr">
         <is>
           <t>RETIRO#AGE#10#1</t>
@@ -33835,21 +31967,9 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>RETIRO EN AGENTES</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>EDUCACIÓN</t>
-        </is>
-      </c>
+      <c r="A526" t="inlineStr"/>
+      <c r="B526" t="inlineStr"/>
+      <c r="C526" t="inlineStr"/>
       <c r="D526" t="inlineStr">
         <is>
           <t>RETIRO#AGE#10#2</t>
@@ -33887,21 +32007,9 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>RETIRO EN AGENTES</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>FIRST</t>
-        </is>
-      </c>
+      <c r="A527" t="inlineStr"/>
+      <c r="B527" t="inlineStr"/>
+      <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr">
         <is>
           <t>RETIRO_F#AGE#10#1</t>
@@ -33939,21 +32047,9 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>RETIRO EN AGENTES</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
+      <c r="A528" t="inlineStr"/>
+      <c r="B528" t="inlineStr"/>
+      <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr">
         <is>
           <t>RETIRO_L#AGE#10#1</t>
@@ -33991,21 +32087,9 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>SEGURO DE TARJETAS PREMIUM</t>
-        </is>
-      </c>
+      <c r="A529" t="inlineStr"/>
+      <c r="B529" t="inlineStr"/>
+      <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr">
         <is>
           <t>1-17R93ZAV#APP#11#1</t>
@@ -34055,21 +32139,9 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>SEGURO PAGOS DIGITALES</t>
-        </is>
-      </c>
+      <c r="A530" t="inlineStr"/>
+      <c r="B530" t="inlineStr"/>
+      <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr">
         <is>
           <t>1-17R93ZB1#APP#11#1</t>
@@ -34119,21 +32191,9 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>SEGURO CELULARES</t>
-        </is>
-      </c>
+      <c r="A531" t="inlineStr"/>
+      <c r="B531" t="inlineStr"/>
+      <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr">
         <is>
           <t>1-1BCTP43B#APP#11#1</t>
@@ -34179,21 +32239,9 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>SEGURO VIVE SAULD</t>
-        </is>
-      </c>
+      <c r="A532" t="inlineStr"/>
+      <c r="B532" t="inlineStr"/>
+      <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr">
         <is>
           <t>1-1BCTP43I#APP#11#1</t>
@@ -34243,21 +32291,9 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>TD DIGITAL</t>
-        </is>
-      </c>
+      <c r="A533" t="inlineStr"/>
+      <c r="B533" t="inlineStr"/>
+      <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr">
         <is>
           <t>1-1HF0QAR5#APP#11#1</t>
@@ -34363,21 +32399,9 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A535" t="inlineStr"/>
+      <c r="B535" t="inlineStr"/>
+      <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr">
         <is>
           <t>1-1JHP8B#APP#11#1</t>
@@ -34427,21 +32451,9 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>FONDOS MUTUOS</t>
-        </is>
-      </c>
+      <c r="A536" t="inlineStr"/>
+      <c r="B536" t="inlineStr"/>
+      <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr">
         <is>
           <t>1-2QIJ2#APP#11#1</t>
@@ -34491,21 +32503,9 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A537" t="inlineStr"/>
+      <c r="B537" t="inlineStr"/>
+      <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr">
         <is>
           <t>1-2QIKK#APP#11#1</t>
@@ -34555,21 +32555,9 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>CUENTA SIMPLE</t>
-        </is>
-      </c>
+      <c r="A538" t="inlineStr"/>
+      <c r="B538" t="inlineStr"/>
+      <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr">
         <is>
           <t>1-2QIKT#APP#11#1</t>
@@ -34619,21 +32607,9 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>DEPOSITO A PLAZO</t>
-        </is>
-      </c>
+      <c r="A539" t="inlineStr"/>
+      <c r="B539" t="inlineStr"/>
+      <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr">
         <is>
           <t>1-2QIM2#APP#11#1</t>
@@ -34683,21 +32659,9 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>CREDITO HIPOTECARIO</t>
-        </is>
-      </c>
+      <c r="A540" t="inlineStr"/>
+      <c r="B540" t="inlineStr"/>
+      <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr">
         <is>
           <t>1-2QINB#APP#11#1</t>
@@ -34747,21 +32711,9 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
+      <c r="A541" t="inlineStr"/>
+      <c r="B541" t="inlineStr"/>
+      <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr">
         <is>
           <t>1-2QIP2#APP#11#1</t>
@@ -34811,21 +32763,9 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>TARJETA ADICIONAL</t>
-        </is>
-      </c>
+      <c r="A542" t="inlineStr"/>
+      <c r="B542" t="inlineStr"/>
+      <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr">
         <is>
           <t>1-2VE9EKL#APP#11#1</t>
@@ -34875,21 +32815,9 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A543" t="inlineStr"/>
+      <c r="B543" t="inlineStr"/>
+      <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr">
         <is>
           <t>1-35L2997#APP#11#1</t>
@@ -34939,21 +32867,9 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>SEGURO 360</t>
-        </is>
-      </c>
+      <c r="A544" t="inlineStr"/>
+      <c r="B544" t="inlineStr"/>
+      <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr">
         <is>
           <t>1-3FGE7FL#APP#11#1</t>
@@ -35003,21 +32919,9 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A545" t="inlineStr"/>
+      <c r="B545" t="inlineStr"/>
+      <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr">
         <is>
           <t>1-7D8Q#APP#11#1</t>
@@ -35067,21 +32971,9 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A546" t="inlineStr"/>
+      <c r="B546" t="inlineStr"/>
+      <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr">
         <is>
           <t>1-8R42A#APP#11#1</t>
@@ -35131,21 +33023,9 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>PRESTAMO EFECTIVO</t>
-        </is>
-      </c>
+      <c r="A547" t="inlineStr"/>
+      <c r="B547" t="inlineStr"/>
+      <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr">
         <is>
           <t>1-8R42G#APP#11#1</t>
@@ -35195,21 +33075,9 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>SEGURO FIT</t>
-        </is>
-      </c>
+      <c r="A548" t="inlineStr"/>
+      <c r="B548" t="inlineStr"/>
+      <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
         <is>
           <t>1-AKYCZ42#APP#11#1</t>
@@ -35259,21 +33127,9 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A549" t="inlineStr"/>
+      <c r="B549" t="inlineStr"/>
+      <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
           <t>1-BXAFM#APP#11#1</t>
@@ -35323,21 +33179,9 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>SEGURO SOAT</t>
-        </is>
-      </c>
+      <c r="A550" t="inlineStr"/>
+      <c r="B550" t="inlineStr"/>
+      <c r="C550" t="inlineStr"/>
       <c r="D550" t="inlineStr">
         <is>
           <t>1-GKG39#APP#11#1</t>
@@ -35387,21 +33231,9 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>SEGURO PROTECCION FULL</t>
-        </is>
-      </c>
+      <c r="A551" t="inlineStr"/>
+      <c r="B551" t="inlineStr"/>
+      <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
         <is>
           <t>1-GKG3F#APP#11#1</t>
@@ -35451,21 +33283,9 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>PAGO AUTOMATICO</t>
-        </is>
-      </c>
+      <c r="A552" t="inlineStr"/>
+      <c r="B552" t="inlineStr"/>
+      <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
           <t>1-ILJO1N#APP#11#1</t>
@@ -35515,21 +33335,9 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>UPGRADE TC</t>
-        </is>
-      </c>
+      <c r="A553" t="inlineStr"/>
+      <c r="B553" t="inlineStr"/>
+      <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr">
         <is>
           <t>1-IP1YJI#APP#11#1</t>
@@ -35631,21 +33439,9 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>COMPRA DE DEUDA</t>
-        </is>
-      </c>
+      <c r="A555" t="inlineStr"/>
+      <c r="B555" t="inlineStr"/>
+      <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
           <t>1-S466PW#APP#11#1</t>
@@ -35695,21 +33491,9 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>CONVENIOS</t>
-        </is>
-      </c>
+      <c r="A556" t="inlineStr"/>
+      <c r="B556" t="inlineStr"/>
+      <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr">
         <is>
           <t>1-S46EFC#APP#11#1</t>
@@ -35759,21 +33543,9 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>SEGURO DE TARJETAS PREMIUM</t>
-        </is>
-      </c>
+      <c r="A557" t="inlineStr"/>
+      <c r="B557" t="inlineStr"/>
+      <c r="C557" t="inlineStr"/>
       <c r="D557" t="inlineStr">
         <is>
           <t>1-17R93ZAV#GMO#11#1</t>
@@ -35823,21 +33595,9 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>SEGURO PAGOS DIGITALES</t>
-        </is>
-      </c>
+      <c r="A558" t="inlineStr"/>
+      <c r="B558" t="inlineStr"/>
+      <c r="C558" t="inlineStr"/>
       <c r="D558" t="inlineStr">
         <is>
           <t>1-17R93ZB1#GMO#11#1</t>
@@ -35887,21 +33647,9 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>SEGURO CELULARES</t>
-        </is>
-      </c>
+      <c r="A559" t="inlineStr"/>
+      <c r="B559" t="inlineStr"/>
+      <c r="C559" t="inlineStr"/>
       <c r="D559" t="inlineStr">
         <is>
           <t>1-1BCTP43B#GMO#11#1</t>
@@ -35947,21 +33695,9 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>SEGURO VIVE SALUD +</t>
-        </is>
-      </c>
+      <c r="A560" t="inlineStr"/>
+      <c r="B560" t="inlineStr"/>
+      <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr">
         <is>
           <t>1-1BCTP43I#GMO#11#1</t>
@@ -36011,21 +33747,9 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>TD DIGITAL</t>
-        </is>
-      </c>
+      <c r="A561" t="inlineStr"/>
+      <c r="B561" t="inlineStr"/>
+      <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr">
         <is>
           <t>1-1HF0QAR5#GMO#11#1</t>
@@ -36075,21 +33799,9 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A562" t="inlineStr"/>
+      <c r="B562" t="inlineStr"/>
+      <c r="C562" t="inlineStr"/>
       <c r="D562" t="inlineStr">
         <is>
           <t>1-1JHP8B#GMO#11#1</t>
@@ -36139,21 +33851,9 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>FONDOS MUTUOS</t>
-        </is>
-      </c>
+      <c r="A563" t="inlineStr"/>
+      <c r="B563" t="inlineStr"/>
+      <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr">
         <is>
           <t>1-2QIJ2#GMO#11#1</t>
@@ -36203,21 +33903,9 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A564" t="inlineStr"/>
+      <c r="B564" t="inlineStr"/>
+      <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr">
         <is>
           <t>1-2QIKK#GMO#11#1</t>
@@ -36267,21 +33955,9 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>CUENTA SIMPLE</t>
-        </is>
-      </c>
+      <c r="A565" t="inlineStr"/>
+      <c r="B565" t="inlineStr"/>
+      <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr">
         <is>
           <t>1-2QIKT#GMO#11#1</t>
@@ -36331,21 +34007,9 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>DEPOSITO A PLAZO</t>
-        </is>
-      </c>
+      <c r="A566" t="inlineStr"/>
+      <c r="B566" t="inlineStr"/>
+      <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr">
         <is>
           <t>1-2QIM2#GMO#11#1</t>
@@ -36395,21 +34059,9 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>CREDITO HIPOTECARIO</t>
-        </is>
-      </c>
+      <c r="A567" t="inlineStr"/>
+      <c r="B567" t="inlineStr"/>
+      <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr">
         <is>
           <t>1-2QINB#GMO#11#1</t>
@@ -36459,21 +34111,9 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
+      <c r="A568" t="inlineStr"/>
+      <c r="B568" t="inlineStr"/>
+      <c r="C568" t="inlineStr"/>
       <c r="D568" t="inlineStr">
         <is>
           <t>1-2QIP2#GMO#11#1</t>
@@ -36523,21 +34163,9 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>TARJETA ADICIONAL</t>
-        </is>
-      </c>
+      <c r="A569" t="inlineStr"/>
+      <c r="B569" t="inlineStr"/>
+      <c r="C569" t="inlineStr"/>
       <c r="D569" t="inlineStr">
         <is>
           <t>1-2VE9EKL#GMO#11#1</t>
@@ -36587,21 +34215,9 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A570" t="inlineStr"/>
+      <c r="B570" t="inlineStr"/>
+      <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr">
         <is>
           <t>1-35L2997#GMO#11#1</t>
@@ -36651,21 +34267,9 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C571" t="inlineStr">
-        <is>
-          <t>SEGURO 360</t>
-        </is>
-      </c>
+      <c r="A571" t="inlineStr"/>
+      <c r="B571" t="inlineStr"/>
+      <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr">
         <is>
           <t>1-3FGE7FL#GMO#11#1</t>
@@ -36715,21 +34319,9 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A572" t="inlineStr"/>
+      <c r="B572" t="inlineStr"/>
+      <c r="C572" t="inlineStr"/>
       <c r="D572" t="inlineStr">
         <is>
           <t>1-7D8Q#GMO#11#1</t>
@@ -36779,21 +34371,9 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A573" t="inlineStr"/>
+      <c r="B573" t="inlineStr"/>
+      <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr">
         <is>
           <t>1-8R42A#GMO#11#1</t>
@@ -36843,21 +34423,9 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C574" t="inlineStr">
-        <is>
-          <t>PRESTAMO EFECTIVO</t>
-        </is>
-      </c>
+      <c r="A574" t="inlineStr"/>
+      <c r="B574" t="inlineStr"/>
+      <c r="C574" t="inlineStr"/>
       <c r="D574" t="inlineStr">
         <is>
           <t>1-8R42G#GMO#11#1</t>
@@ -36907,21 +34475,9 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C575" t="inlineStr">
-        <is>
-          <t>SEGURO FIT</t>
-        </is>
-      </c>
+      <c r="A575" t="inlineStr"/>
+      <c r="B575" t="inlineStr"/>
+      <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr">
         <is>
           <t>1-AKYCZ42#GMO#11#1</t>
@@ -36971,21 +34527,9 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C576" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A576" t="inlineStr"/>
+      <c r="B576" t="inlineStr"/>
+      <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr">
         <is>
           <t>1-BXAFM#GMO#11#1</t>
@@ -37035,21 +34579,9 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C577" t="inlineStr">
-        <is>
-          <t>SEGURO SOAT</t>
-        </is>
-      </c>
+      <c r="A577" t="inlineStr"/>
+      <c r="B577" t="inlineStr"/>
+      <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr">
         <is>
           <t>1-GKG39#GMO#11#1</t>
@@ -37099,21 +34631,9 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C578" t="inlineStr">
-        <is>
-          <t>SEGURO PROTECCION FULL</t>
-        </is>
-      </c>
+      <c r="A578" t="inlineStr"/>
+      <c r="B578" t="inlineStr"/>
+      <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
           <t>1-GKG3F#GMO#11#1</t>
@@ -37163,21 +34683,9 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>PAGO AUTOMATICO</t>
-        </is>
-      </c>
+      <c r="A579" t="inlineStr"/>
+      <c r="B579" t="inlineStr"/>
+      <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr">
         <is>
           <t>1-ILJO1N#GMO#11#1</t>
@@ -37227,21 +34735,9 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C580" t="inlineStr">
-        <is>
-          <t>UPGRADE TC</t>
-        </is>
-      </c>
+      <c r="A580" t="inlineStr"/>
+      <c r="B580" t="inlineStr"/>
+      <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr">
         <is>
           <t>1-IP1YJI#GMO#11#1</t>
@@ -37291,21 +34787,9 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C581" t="inlineStr">
-        <is>
-          <t>COMPRA DE DEUDA</t>
-        </is>
-      </c>
+      <c r="A581" t="inlineStr"/>
+      <c r="B581" t="inlineStr"/>
+      <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr">
         <is>
           <t>1-S466PW#GMO#11#1</t>
@@ -37355,21 +34839,9 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>PRODUCTOS PARA TI</t>
-        </is>
-      </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C582" t="inlineStr">
-        <is>
-          <t>CONVENIOS</t>
-        </is>
-      </c>
+      <c r="A582" t="inlineStr"/>
+      <c r="B582" t="inlineStr"/>
+      <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr">
         <is>
           <t>1-S46EFC#GMO#11#1</t>
@@ -37419,21 +34891,9 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C583" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A583" t="inlineStr"/>
+      <c r="B583" t="inlineStr"/>
+      <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr">
         <is>
           <t>1-1UWHSB#DF#ABO#12#HTML#1</t>
@@ -37471,21 +34931,9 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C584" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A584" t="inlineStr"/>
+      <c r="B584" t="inlineStr"/>
+      <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
           <t>1-1UWHSB#DF#ABO#12#PUSH#1</t>
@@ -37523,21 +34971,9 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B585" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C585" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A585" t="inlineStr"/>
+      <c r="B585" t="inlineStr"/>
+      <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr">
         <is>
           <t>1-2QIKK#DF#ABO#12#HTML#1</t>
@@ -37575,21 +35011,9 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B586" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C586" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A586" t="inlineStr"/>
+      <c r="B586" t="inlineStr"/>
+      <c r="C586" t="inlineStr"/>
       <c r="D586" t="inlineStr">
         <is>
           <t>1-2QIKK#DF#ABO#12#PUSH#1</t>
@@ -37627,21 +35051,9 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A587" t="inlineStr"/>
+      <c r="B587" t="inlineStr"/>
+      <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
           <t>1-2QIKK#R1#ABO#12#HTML#1</t>
@@ -37679,21 +35091,9 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B588" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C588" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A588" t="inlineStr"/>
+      <c r="B588" t="inlineStr"/>
+      <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr">
         <is>
           <t>1-2QIKK#R1#ABO#12#PUSH#1</t>
@@ -37731,21 +35131,9 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A589" t="inlineStr"/>
+      <c r="B589" t="inlineStr"/>
+      <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr">
         <is>
           <t>1-2QIKK#R2#ABO#12#HTML#1</t>
@@ -37783,21 +35171,9 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A590" t="inlineStr"/>
+      <c r="B590" t="inlineStr"/>
+      <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
         <is>
           <t>1-2QIKK#R2#ABO#12#PUSH#1</t>
@@ -37835,21 +35211,9 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A591" t="inlineStr"/>
+      <c r="B591" t="inlineStr"/>
+      <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
           <t>1-2QIKK#R3#ABO#12#HTML#1</t>
@@ -37887,21 +35251,9 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A592" t="inlineStr"/>
+      <c r="B592" t="inlineStr"/>
+      <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr">
         <is>
           <t>1-2QIKK#R3#ABO#12#PUSH#1</t>
@@ -37939,21 +35291,9 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A593" t="inlineStr"/>
+      <c r="B593" t="inlineStr"/>
+      <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
           <t>1-2QIKK#R4#ABO#12#HTML#1</t>
@@ -37991,21 +35331,9 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A594" t="inlineStr"/>
+      <c r="B594" t="inlineStr"/>
+      <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
           <t>1-2QIKK#R4#ABO#12#PUSH#1</t>
@@ -38043,21 +35371,9 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A595" t="inlineStr"/>
+      <c r="B595" t="inlineStr"/>
+      <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
           <t>1-2QIKK#R5#ABO#12#HTML#1</t>
@@ -38095,21 +35411,9 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A596" t="inlineStr"/>
+      <c r="B596" t="inlineStr"/>
+      <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
           <t>1-2QIKK#R5#ABO#12#PUSH#1</t>
@@ -38147,21 +35451,9 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A597" t="inlineStr"/>
+      <c r="B597" t="inlineStr"/>
+      <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
           <t>1-35L2997#DF#ABO#12#HTML#1</t>
@@ -38199,21 +35491,9 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A598" t="inlineStr"/>
+      <c r="B598" t="inlineStr"/>
+      <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
           <t>1-35L2997#DF#ABO#12#PUSH#1</t>
@@ -38251,21 +35531,9 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A599" t="inlineStr"/>
+      <c r="B599" t="inlineStr"/>
+      <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
           <t>1-35L2997#R1#ABO#12#HTML#1</t>
@@ -38303,21 +35571,9 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C600" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A600" t="inlineStr"/>
+      <c r="B600" t="inlineStr"/>
+      <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
           <t>1-35L2997#R1#ABO#12#PUSH#1</t>
@@ -38355,21 +35611,9 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A601" t="inlineStr"/>
+      <c r="B601" t="inlineStr"/>
+      <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
           <t>1-35L2997#R2#ABO#12#HTML#1</t>
@@ -38407,21 +35651,9 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A602" t="inlineStr"/>
+      <c r="B602" t="inlineStr"/>
+      <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
           <t>1-35L2997#R3#ABO#12#HTML#1</t>
@@ -38459,21 +35691,9 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A603" t="inlineStr"/>
+      <c r="B603" t="inlineStr"/>
+      <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
           <t>1-35L2997#R4#ABO#12#HTML#1</t>
@@ -38511,21 +35731,9 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>ABONO ATIPICO</t>
-        </is>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A604" t="inlineStr"/>
+      <c r="B604" t="inlineStr"/>
+      <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
           <t>1-35L2997#R5#ABO#12#HTML#1</t>
@@ -38563,21 +35771,9 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A605" t="inlineStr"/>
+      <c r="B605" t="inlineStr"/>
+      <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
           <t>DGC#D#ATM#13#SMS#1</t>
@@ -38615,21 +35811,9 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B606" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A606" t="inlineStr"/>
+      <c r="B606" t="inlineStr"/>
+      <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
           <t>DGC#ND#ATM#13#PUSH#1</t>
@@ -38667,21 +35851,9 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A607" t="inlineStr"/>
+      <c r="B607" t="inlineStr"/>
+      <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
           <t>DGC#ND#ATM#13#SMS#1</t>
@@ -38719,21 +35891,9 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>CONSUMO ONLINE</t>
-        </is>
-      </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>DIGITALIZACIÓN</t>
-        </is>
-      </c>
+      <c r="A608" t="inlineStr"/>
+      <c r="B608" t="inlineStr"/>
+      <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr">
         <is>
           <t>DGC#ECOM#13#1</t>
@@ -38775,21 +35935,9 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C609" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A609" t="inlineStr"/>
+      <c r="B609" t="inlineStr"/>
+      <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr">
         <is>
           <t>DGC#ECOM#13#2</t>
@@ -38831,21 +35979,9 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B610" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C610" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A610" t="inlineStr"/>
+      <c r="B610" t="inlineStr"/>
+      <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr">
         <is>
           <t>CONSULTA#AGE#14#1</t>
@@ -38887,21 +36023,9 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C611" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A611" t="inlineStr"/>
+      <c r="B611" t="inlineStr"/>
+      <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr">
         <is>
           <t>CONSULTA#AGE#14#2</t>
@@ -38943,21 +36067,9 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A612" t="inlineStr"/>
+      <c r="B612" t="inlineStr"/>
+      <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr">
         <is>
           <t>PTL#ECOM#15#1</t>
@@ -38999,21 +36111,9 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C613" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A613" t="inlineStr"/>
+      <c r="B613" t="inlineStr"/>
+      <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr">
         <is>
           <t>PTL#ECOM#15#PUSH#1</t>
@@ -39055,21 +36155,9 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>PREVENTIVO TOPE DE LÍNEA</t>
-        </is>
-      </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C614" t="inlineStr">
-        <is>
-          <t>EDUCACIÓN</t>
-        </is>
-      </c>
+      <c r="A614" t="inlineStr"/>
+      <c r="B614" t="inlineStr"/>
+      <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr">
         <is>
           <t>PTL#POS#15#1</t>
@@ -39111,21 +36199,9 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A615" t="inlineStr"/>
+      <c r="B615" t="inlineStr"/>
+      <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr">
         <is>
           <t>PTL#POS#15#PUSH#1</t>
@@ -39167,21 +36243,9 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C616" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A616" t="inlineStr"/>
+      <c r="B616" t="inlineStr"/>
+      <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#1#1</t>
@@ -39223,21 +36287,9 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C617" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A617" t="inlineStr"/>
+      <c r="B617" t="inlineStr"/>
+      <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#1#2</t>
@@ -39279,21 +36331,9 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C618" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A618" t="inlineStr"/>
+      <c r="B618" t="inlineStr"/>
+      <c r="C618" t="inlineStr"/>
       <c r="D618" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#2#1</t>
@@ -39335,21 +36375,9 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A619" t="inlineStr"/>
+      <c r="B619" t="inlineStr"/>
+      <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#2#2</t>
@@ -39391,21 +36419,9 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A620" t="inlineStr"/>
+      <c r="B620" t="inlineStr"/>
+      <c r="C620" t="inlineStr"/>
       <c r="D620" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#3#1</t>
@@ -39447,21 +36463,9 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C621" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A621" t="inlineStr"/>
+      <c r="B621" t="inlineStr"/>
+      <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#3#2</t>
@@ -39503,21 +36507,9 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C622" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A622" t="inlineStr"/>
+      <c r="B622" t="inlineStr"/>
+      <c r="C622" t="inlineStr"/>
       <c r="D622" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#4#1</t>
@@ -39559,21 +36551,9 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A623" t="inlineStr"/>
+      <c r="B623" t="inlineStr"/>
+      <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#4#2</t>
@@ -39615,21 +36595,9 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C624" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A624" t="inlineStr"/>
+      <c r="B624" t="inlineStr"/>
+      <c r="C624" t="inlineStr"/>
       <c r="D624" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#5#1</t>
@@ -39671,21 +36639,9 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C625" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A625" t="inlineStr"/>
+      <c r="B625" t="inlineStr"/>
+      <c r="C625" t="inlineStr"/>
       <c r="D625" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#5#2</t>
@@ -39727,21 +36683,9 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B626" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C626" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A626" t="inlineStr"/>
+      <c r="B626" t="inlineStr"/>
+      <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#6#1</t>
@@ -39783,21 +36727,9 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B627" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C627" t="inlineStr">
-        <is>
-          <t>USO CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A627" t="inlineStr"/>
+      <c r="B627" t="inlineStr"/>
+      <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
           <t>1-7D8Q#UCS#16#6#2</t>
@@ -39839,21 +36771,9 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B628" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C628" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A628" t="inlineStr"/>
+      <c r="B628" t="inlineStr"/>
+      <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
           <t>1-1JHP8B#APP#17#1</t>
@@ -39895,21 +36815,9 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>VENTA CROSS SCORE</t>
-        </is>
-      </c>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C629" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A629" t="inlineStr"/>
+      <c r="B629" t="inlineStr"/>
+      <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr">
         <is>
           <t>1-1JHP8B#APP#17#PUSH#1</t>
@@ -39951,21 +36859,9 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>VENTA CROSS SCORE</t>
-        </is>
-      </c>
-      <c r="B630" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C630" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
+      <c r="A630" t="inlineStr"/>
+      <c r="B630" t="inlineStr"/>
+      <c r="C630" t="inlineStr"/>
       <c r="D630" t="inlineStr">
         <is>
           <t>1-2QIP2#APP#17#1</t>
@@ -40007,21 +36903,9 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>VENTA CROSS SCORE</t>
-        </is>
-      </c>
-      <c r="B631" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C631" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
+      <c r="A631" t="inlineStr"/>
+      <c r="B631" t="inlineStr"/>
+      <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr">
         <is>
           <t>1-2QIP2#APP#17#PUSH#1</t>
@@ -40063,21 +36947,9 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C632" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A632" t="inlineStr"/>
+      <c r="B632" t="inlineStr"/>
+      <c r="C632" t="inlineStr"/>
       <c r="D632" t="inlineStr">
         <is>
           <t>1-8R42A#APP#17#1</t>
@@ -40119,21 +36991,9 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>VENTA CROSS SCORE</t>
-        </is>
-      </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C633" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A633" t="inlineStr"/>
+      <c r="B633" t="inlineStr"/>
+      <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr">
         <is>
           <t>1-8R42A#APP#17#PUSH#1</t>
@@ -40175,21 +37035,9 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B634" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C634" t="inlineStr">
-        <is>
-          <t>PRESTAMO EFECTIVO</t>
-        </is>
-      </c>
+      <c r="A634" t="inlineStr"/>
+      <c r="B634" t="inlineStr"/>
+      <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
           <t>1-8R42G#APP#17#1</t>
@@ -40231,21 +37079,9 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>PRESTAMO EFECTIVO</t>
-        </is>
-      </c>
+      <c r="A635" t="inlineStr"/>
+      <c r="B635" t="inlineStr"/>
+      <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr">
         <is>
           <t>1-8R42G#APP#17#PUSH#1</t>
@@ -40287,21 +37123,9 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>VENTA CROSS SCORE</t>
-        </is>
-      </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A636" t="inlineStr"/>
+      <c r="B636" t="inlineStr"/>
+      <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
           <t>1-BXAFM#APP#17#1</t>
@@ -40343,21 +37167,9 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C637" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A637" t="inlineStr"/>
+      <c r="B637" t="inlineStr"/>
+      <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
           <t>1-BXAFM#APP#17#PUSH#1</t>
@@ -40399,21 +37211,9 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>VENTA CROSS SCORE</t>
-        </is>
-      </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A638" t="inlineStr"/>
+      <c r="B638" t="inlineStr"/>
+      <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr">
         <is>
           <t>1-1UWIDW#RET#19#1</t>
@@ -40455,21 +37255,9 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B639" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr">
-        <is>
-          <t>TARJETA DIGITAL</t>
-        </is>
-      </c>
+      <c r="A639" t="inlineStr"/>
+      <c r="B639" t="inlineStr"/>
+      <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
           <t>1-1HF0QAR5#APP#20#1</t>
@@ -40519,21 +37307,9 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A640" t="inlineStr"/>
+      <c r="B640" t="inlineStr"/>
+      <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
           <t>1-1JHP8B#APP#20#1</t>
@@ -40583,21 +37359,9 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B641" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C641" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A641" t="inlineStr"/>
+      <c r="B641" t="inlineStr"/>
+      <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
           <t>1-2QIKK#APP#20#1</t>
@@ -40647,21 +37411,9 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C642" t="inlineStr">
-        <is>
-          <t>CUENTA SIMPLE</t>
-        </is>
-      </c>
+      <c r="A642" t="inlineStr"/>
+      <c r="B642" t="inlineStr"/>
+      <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
           <t>1-2QIKT#APP#20#1</t>
@@ -40711,21 +37463,9 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C643" t="inlineStr">
-        <is>
-          <t>DEPOSITO A PLAZO</t>
-        </is>
-      </c>
+      <c r="A643" t="inlineStr"/>
+      <c r="B643" t="inlineStr"/>
+      <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
           <t>1-2QIM2#APP#20#1</t>
@@ -40775,21 +37515,9 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B644" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C644" t="inlineStr">
-        <is>
-          <t>CREDITO HIPOTECARIO</t>
-        </is>
-      </c>
+      <c r="A644" t="inlineStr"/>
+      <c r="B644" t="inlineStr"/>
+      <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
           <t>1-2QINB#APP#20#1</t>
@@ -40839,21 +37567,9 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
+      <c r="A645" t="inlineStr"/>
+      <c r="B645" t="inlineStr"/>
+      <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
           <t>1-2QIP2#APP#20#1</t>
@@ -40903,21 +37619,9 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr">
-        <is>
-          <t>TARJETA ADICIONAL</t>
-        </is>
-      </c>
+      <c r="A646" t="inlineStr"/>
+      <c r="B646" t="inlineStr"/>
+      <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
           <t>1-2VE9EKL#APP#20#1</t>
@@ -40967,21 +37671,9 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C647" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A647" t="inlineStr"/>
+      <c r="B647" t="inlineStr"/>
+      <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
           <t>1-35L2997#APP#20#1</t>
@@ -41031,21 +37723,9 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C648" t="inlineStr">
-        <is>
-          <t>SEGURO 360</t>
-        </is>
-      </c>
+      <c r="A648" t="inlineStr"/>
+      <c r="B648" t="inlineStr"/>
+      <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
           <t>1-3FGE7FL#APP#20#1</t>
@@ -41095,21 +37775,9 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C649" t="inlineStr">
-        <is>
-          <t>CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A649" t="inlineStr"/>
+      <c r="B649" t="inlineStr"/>
+      <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
           <t>1-7D8Q#APP#20#1</t>
@@ -41159,21 +37827,9 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A650" t="inlineStr"/>
+      <c r="B650" t="inlineStr"/>
+      <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
           <t>1-8R42A#APP#20#1</t>
@@ -41223,21 +37879,9 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C651" t="inlineStr">
-        <is>
-          <t>PRESTAMO EFECTIVO</t>
-        </is>
-      </c>
+      <c r="A651" t="inlineStr"/>
+      <c r="B651" t="inlineStr"/>
+      <c r="C651" t="inlineStr"/>
       <c r="D651" t="inlineStr">
         <is>
           <t>1-8R42G#APP#20#1</t>
@@ -41287,21 +37931,9 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
-        <is>
-          <t>SEGURO FIT</t>
-        </is>
-      </c>
+      <c r="A652" t="inlineStr"/>
+      <c r="B652" t="inlineStr"/>
+      <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
           <t>1-AKYCZ42#APP#20#1</t>
@@ -41351,21 +37983,9 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A653" t="inlineStr"/>
+      <c r="B653" t="inlineStr"/>
+      <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
           <t>1-BXAFM#APP#20#1</t>
@@ -41415,21 +38035,9 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
-        <is>
-          <t>SEGURO SOAT</t>
-        </is>
-      </c>
+      <c r="A654" t="inlineStr"/>
+      <c r="B654" t="inlineStr"/>
+      <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
           <t>1-GKG39#APP#20#1</t>
@@ -41479,21 +38087,9 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B655" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C655" t="inlineStr">
-        <is>
-          <t>PAGO AUTOMATICO</t>
-        </is>
-      </c>
+      <c r="A655" t="inlineStr"/>
+      <c r="B655" t="inlineStr"/>
+      <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
           <t>1-ILJO1N#APP#20#1</t>
@@ -41543,21 +38139,9 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B656" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C656" t="inlineStr">
-        <is>
-          <t>UPGRADE</t>
-        </is>
-      </c>
+      <c r="A656" t="inlineStr"/>
+      <c r="B656" t="inlineStr"/>
+      <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr">
         <is>
           <t>1-IP1YJI#APP#20#1</t>
@@ -41603,21 +38187,9 @@
       </c>
     </row>
     <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B657" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C657" t="inlineStr">
-        <is>
-          <t>CONVENIO</t>
-        </is>
-      </c>
+      <c r="A657" t="inlineStr"/>
+      <c r="B657" t="inlineStr"/>
+      <c r="C657" t="inlineStr"/>
       <c r="D657" t="inlineStr">
         <is>
           <t>1-S46EFC#APP#20#1</t>
@@ -41667,21 +38239,9 @@
       </c>
     </row>
     <row r="658">
-      <c r="A658" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B658" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C658" t="inlineStr">
-        <is>
-          <t>ALCANCIA VIRTUAL</t>
-        </is>
-      </c>
+      <c r="A658" t="inlineStr"/>
+      <c r="B658" t="inlineStr"/>
+      <c r="C658" t="inlineStr"/>
       <c r="D658" t="inlineStr">
         <is>
           <t>ALCV#APP#20#1</t>
@@ -41731,21 +38291,9 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>MANITO LEGO</t>
-        </is>
-      </c>
-      <c r="B659" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C659" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A659" t="inlineStr"/>
+      <c r="B659" t="inlineStr"/>
+      <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr">
         <is>
           <t>ITMD#APP#20#1</t>
@@ -41787,21 +38335,9 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C660" t="inlineStr">
-        <is>
-          <t>INCREMENTO DE LINEA</t>
-        </is>
-      </c>
+      <c r="A660" t="inlineStr"/>
+      <c r="B660" t="inlineStr"/>
+      <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr">
         <is>
           <t>1-1JHP8B#APP#21#1</t>
@@ -41851,21 +38387,9 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B661" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
-        <is>
-          <t>CUENTA MILLONARIA</t>
-        </is>
-      </c>
+      <c r="A661" t="inlineStr"/>
+      <c r="B661" t="inlineStr"/>
+      <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr">
         <is>
           <t>1-2QIKK#APP#21#1</t>
@@ -41915,21 +38439,9 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C662" t="inlineStr">
-        <is>
-          <t>CUENTA SIMPLE</t>
-        </is>
-      </c>
+      <c r="A662" t="inlineStr"/>
+      <c r="B662" t="inlineStr"/>
+      <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
           <t>1-2QIKT#APP#21#1</t>
@@ -41979,21 +38491,9 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr">
-        <is>
-          <t>DEPOSITO A PLAZO</t>
-        </is>
-      </c>
+      <c r="A663" t="inlineStr"/>
+      <c r="B663" t="inlineStr"/>
+      <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
           <t>1-2QIM2#APP#21#1</t>
@@ -42043,21 +38543,9 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr">
-        <is>
-          <t>CREDITO HIPOTECARIO</t>
-        </is>
-      </c>
+      <c r="A664" t="inlineStr"/>
+      <c r="B664" t="inlineStr"/>
+      <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr">
         <is>
           <t>1-2QINB#APP#21#1</t>
@@ -42107,21 +38595,9 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C665" t="inlineStr">
-        <is>
-          <t>ADELANTO DE SUELDO</t>
-        </is>
-      </c>
+      <c r="A665" t="inlineStr"/>
+      <c r="B665" t="inlineStr"/>
+      <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr">
         <is>
           <t>1-2QIP2#APP#21#1</t>
@@ -42171,21 +38647,9 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C666" t="inlineStr">
-        <is>
-          <t>TARJETA ADICIONAL</t>
-        </is>
-      </c>
+      <c r="A666" t="inlineStr"/>
+      <c r="B666" t="inlineStr"/>
+      <c r="C666" t="inlineStr"/>
       <c r="D666" t="inlineStr">
         <is>
           <t>1-2VE9EKL#APP#21#1</t>
@@ -42235,21 +38699,9 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr">
-        <is>
-          <t>CUENTA SUPER TASA</t>
-        </is>
-      </c>
+      <c r="A667" t="inlineStr"/>
+      <c r="B667" t="inlineStr"/>
+      <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
           <t>1-35L2997#APP#21#1</t>
@@ -42299,21 +38751,9 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C668" t="inlineStr">
-        <is>
-          <t>SEGURO 360</t>
-        </is>
-      </c>
+      <c r="A668" t="inlineStr"/>
+      <c r="B668" t="inlineStr"/>
+      <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr">
         <is>
           <t>1-3FGE7FL#APP#21#1</t>
@@ -42363,21 +38803,9 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C669" t="inlineStr">
-        <is>
-          <t>CUENTA SUELDO</t>
-        </is>
-      </c>
+      <c r="A669" t="inlineStr"/>
+      <c r="B669" t="inlineStr"/>
+      <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr">
         <is>
           <t>1-7D8Q#APP#21#1</t>
@@ -42427,21 +38855,9 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C670" t="inlineStr">
-        <is>
-          <t>EXTRACASH</t>
-        </is>
-      </c>
+      <c r="A670" t="inlineStr"/>
+      <c r="B670" t="inlineStr"/>
+      <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
           <t>1-8R42A#APP#21#1</t>
@@ -42491,21 +38907,9 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C671" t="inlineStr">
-        <is>
-          <t>PRESTAMO EFECTIVO</t>
-        </is>
-      </c>
+      <c r="A671" t="inlineStr"/>
+      <c r="B671" t="inlineStr"/>
+      <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr">
         <is>
           <t>1-8R42G#APP#21#1</t>
@@ -42555,21 +38959,9 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C672" t="inlineStr">
-        <is>
-          <t>SEGURO FIT</t>
-        </is>
-      </c>
+      <c r="A672" t="inlineStr"/>
+      <c r="B672" t="inlineStr"/>
+      <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr">
         <is>
           <t>1-AKYCZ42#APP#21#1</t>
@@ -42619,21 +39011,9 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C673" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A673" t="inlineStr"/>
+      <c r="B673" t="inlineStr"/>
+      <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr">
         <is>
           <t>1-BXAFM#APP#21#1</t>
@@ -42683,21 +39063,9 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B674" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C674" t="inlineStr">
-        <is>
-          <t>PAGO AUTOMATICO</t>
-        </is>
-      </c>
+      <c r="A674" t="inlineStr"/>
+      <c r="B674" t="inlineStr"/>
+      <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr">
         <is>
           <t>1-ILJO1N#APP#21#1</t>
@@ -42747,21 +39115,9 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C675" t="inlineStr">
-        <is>
-          <t>UPGRADE</t>
-        </is>
-      </c>
+      <c r="A675" t="inlineStr"/>
+      <c r="B675" t="inlineStr"/>
+      <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr">
         <is>
           <t>1-IP1YJI#APP#21#1</t>
@@ -42807,21 +39163,9 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C676" t="inlineStr">
-        <is>
-          <t>CONVENIOS</t>
-        </is>
-      </c>
+      <c r="A676" t="inlineStr"/>
+      <c r="B676" t="inlineStr"/>
+      <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr">
         <is>
           <t>1-S46EFC#APP#21#1</t>
@@ -42871,21 +39215,9 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C677" t="inlineStr">
-        <is>
-          <t>ALCANCIA VIRTUAL</t>
-        </is>
-      </c>
+      <c r="A677" t="inlineStr"/>
+      <c r="B677" t="inlineStr"/>
+      <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr">
         <is>
           <t>ALCV#APP#21#1</t>
@@ -42935,21 +39267,9 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" t="inlineStr">
-        <is>
-          <t>VENTA CROSS LEGO</t>
-        </is>
-      </c>
-      <c r="B678" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C678" t="inlineStr">
-        <is>
-          <t>ITEM DEFAULT</t>
-        </is>
-      </c>
+      <c r="A678" t="inlineStr"/>
+      <c r="B678" t="inlineStr"/>
+      <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
           <t>ITMD#APP#21#1</t>
@@ -42991,21 +39311,9 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" t="inlineStr">
-        <is>
-          <t>PREVENTIVO ME VOY DE VIAJE</t>
-        </is>
-      </c>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C679" t="inlineStr">
-        <is>
-          <t>PREVENTIVO ME VOY DE VIAJE</t>
-        </is>
-      </c>
+      <c r="A679" t="inlineStr"/>
+      <c r="B679" t="inlineStr"/>
+      <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr">
         <is>
           <t>BCE#PCE#23#BI#PUSH#1</t>
@@ -43047,21 +39355,9 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B680" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C680" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A680" t="inlineStr"/>
+      <c r="B680" t="inlineStr"/>
+      <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
           <t>BCE#PCE#23#BI#SMS#1</t>
@@ -43107,21 +39403,9 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>CANCELACION</t>
-        </is>
-      </c>
-      <c r="B681" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C681" t="inlineStr">
-        <is>
-          <t>PLAZO FIJO</t>
-        </is>
-      </c>
+      <c r="A681" t="inlineStr"/>
+      <c r="B681" t="inlineStr"/>
+      <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
           <t>CPF#ECOM#29#PUSH</t>
@@ -43159,21 +39443,9 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>CANCELACION</t>
-        </is>
-      </c>
-      <c r="B682" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C682" t="inlineStr">
-        <is>
-          <t>PLAZO FIJO</t>
-        </is>
-      </c>
+      <c r="A682" t="inlineStr"/>
+      <c r="B682" t="inlineStr"/>
+      <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
           <t>CPF#ECOM#29#SMS#1</t>
@@ -43215,21 +39487,9 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>CANCELACION</t>
-        </is>
-      </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C683" t="inlineStr">
-        <is>
-          <t>PLAZO FIJO</t>
-        </is>
-      </c>
+      <c r="A683" t="inlineStr"/>
+      <c r="B683" t="inlineStr"/>
+      <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
           <t>CPF#TDA#29#PUSH</t>
@@ -43267,21 +39527,9 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>CANCELACION</t>
-        </is>
-      </c>
-      <c r="B684" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C684" t="inlineStr">
-        <is>
-          <t>PLAZO FIJO</t>
-        </is>
-      </c>
+      <c r="A684" t="inlineStr"/>
+      <c r="B684" t="inlineStr"/>
+      <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
           <t>CPF#TDA#29#SMS#1</t>
@@ -43323,21 +39571,9 @@
       </c>
     </row>
     <row r="685">
-      <c r="A685" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B685" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C685" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A685" t="inlineStr"/>
+      <c r="B685" t="inlineStr"/>
+      <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
           <t>ATMD#ATM#30#PUSH#G1#1</t>
@@ -43379,21 +39615,9 @@
       </c>
     </row>
     <row r="686">
-      <c r="A686" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B686" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C686" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A686" t="inlineStr"/>
+      <c r="B686" t="inlineStr"/>
+      <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
           <t>ATMD#ATM#30#PUSH#G2#1</t>
@@ -43435,21 +39659,9 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B687" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C687" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A687" t="inlineStr"/>
+      <c r="B687" t="inlineStr"/>
+      <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
           <t>ATMD#ATM#30#PUSH#G3#1</t>
@@ -43491,21 +39703,9 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B688" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C688" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A688" t="inlineStr"/>
+      <c r="B688" t="inlineStr"/>
+      <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
           <t>ATMD#ATM#30#PUSH#G4#1</t>
@@ -43547,21 +39747,9 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B689" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C689" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A689" t="inlineStr"/>
+      <c r="B689" t="inlineStr"/>
+      <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
           <t>ATMD#ATM#30#SMS#G1#1</t>
@@ -43603,21 +39791,9 @@
       </c>
     </row>
     <row r="690">
-      <c r="A690" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B690" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C690" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A690" t="inlineStr"/>
+      <c r="B690" t="inlineStr"/>
+      <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr">
         <is>
           <t>ATMD#ATM#30#SMS#G2#1</t>
@@ -43659,21 +39835,9 @@
       </c>
     </row>
     <row r="691">
-      <c r="A691" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B691" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C691" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A691" t="inlineStr"/>
+      <c r="B691" t="inlineStr"/>
+      <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
           <t>ATMD#ATM#30#SMS#G3#1</t>
@@ -43715,21 +39879,9 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B692" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C692" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A692" t="inlineStr"/>
+      <c r="B692" t="inlineStr"/>
+      <c r="C692" t="inlineStr"/>
       <c r="D692" t="inlineStr">
         <is>
           <t>ATMD#ATM#30#SMS#G4#1</t>
@@ -43771,21 +39923,9 @@
       </c>
     </row>
     <row r="693">
-      <c r="A693" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WALLE </t>
-        </is>
-      </c>
-      <c r="B693" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C693" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A693" t="inlineStr"/>
+      <c r="B693" t="inlineStr"/>
+      <c r="C693" t="inlineStr"/>
       <c r="D693" t="inlineStr">
         <is>
           <t>1-BXAFM#TDA#32#PUSH#C#1</t>
@@ -43827,21 +39967,9 @@
       </c>
     </row>
     <row r="694">
-      <c r="A694" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WALLE </t>
-        </is>
-      </c>
-      <c r="B694" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C694" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A694" t="inlineStr"/>
+      <c r="B694" t="inlineStr"/>
+      <c r="C694" t="inlineStr"/>
       <c r="D694" t="inlineStr">
         <is>
           <t>1-BXAFM#TDA#32#PUSH#C#2</t>
@@ -43883,21 +40011,9 @@
       </c>
     </row>
     <row r="695">
-      <c r="A695" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WALLE </t>
-        </is>
-      </c>
-      <c r="B695" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C695" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A695" t="inlineStr"/>
+      <c r="B695" t="inlineStr"/>
+      <c r="C695" t="inlineStr"/>
       <c r="D695" t="inlineStr">
         <is>
           <t>1-BXAFM#TDA#32#SMS#C#1</t>
@@ -43939,21 +40055,9 @@
       </c>
     </row>
     <row r="696">
-      <c r="A696" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WALLE </t>
-        </is>
-      </c>
-      <c r="B696" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C696" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A696" t="inlineStr"/>
+      <c r="B696" t="inlineStr"/>
+      <c r="C696" t="inlineStr"/>
       <c r="D696" t="inlineStr">
         <is>
           <t>1-BXAFM#TDA#32#SMS#C#2</t>
@@ -43995,21 +40099,9 @@
       </c>
     </row>
     <row r="697">
-      <c r="A697" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WALLE </t>
-        </is>
-      </c>
-      <c r="B697" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C697" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A697" t="inlineStr"/>
+      <c r="B697" t="inlineStr"/>
+      <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr">
         <is>
           <t>1-BXAFM#TDA#32#SMS#NC#1</t>
@@ -44051,21 +40143,9 @@
       </c>
     </row>
     <row r="698">
-      <c r="A698" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WALLE </t>
-        </is>
-      </c>
-      <c r="B698" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C698" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A698" t="inlineStr"/>
+      <c r="B698" t="inlineStr"/>
+      <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr">
         <is>
           <t>1-BXAFM#TDA#32#SMS#NC#2</t>
@@ -44107,21 +40187,9 @@
       </c>
     </row>
     <row r="699">
-      <c r="A699" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B699" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C699" t="inlineStr">
-        <is>
-          <t>CXI CONFIRMACIÓN</t>
-        </is>
-      </c>
+      <c r="A699" t="inlineStr"/>
+      <c r="B699" t="inlineStr"/>
+      <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr">
         <is>
           <t>ACTIVE#T6#SMS#100</t>
@@ -44159,21 +40227,9 @@
       </c>
     </row>
     <row r="700">
-      <c r="A700" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B700" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C700" t="inlineStr">
-        <is>
-          <t>CXI CONFIRMACIÓN</t>
-        </is>
-      </c>
+      <c r="A700" t="inlineStr"/>
+      <c r="B700" t="inlineStr"/>
+      <c r="C700" t="inlineStr"/>
       <c r="D700" t="inlineStr">
         <is>
           <t>ISACTIVATED#T6#SMS#100</t>
@@ -44211,21 +40267,9 @@
       </c>
     </row>
     <row r="701">
-      <c r="A701" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B701" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C701" t="inlineStr">
-        <is>
-          <t>CXI CONFIRMACIÓN</t>
-        </is>
-      </c>
+      <c r="A701" t="inlineStr"/>
+      <c r="B701" t="inlineStr"/>
+      <c r="C701" t="inlineStr"/>
       <c r="D701" t="inlineStr">
         <is>
           <t>NOACTIVE#T6#SMS#100</t>
@@ -44263,21 +40307,9 @@
       </c>
     </row>
     <row r="702">
-      <c r="A702" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B702" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C702" t="inlineStr">
-        <is>
-          <t>CXI CONFIRMACIÓN</t>
-        </is>
-      </c>
+      <c r="A702" t="inlineStr"/>
+      <c r="B702" t="inlineStr"/>
+      <c r="C702" t="inlineStr"/>
       <c r="D702" t="inlineStr">
         <is>
           <t>ACTIVE#Z6#SMS#101</t>
@@ -44315,21 +40347,9 @@
       </c>
     </row>
     <row r="703">
-      <c r="A703" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
-      <c r="B703" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C703" t="inlineStr">
-        <is>
-          <t>#N/D</t>
-        </is>
-      </c>
+      <c r="A703" t="inlineStr"/>
+      <c r="B703" t="inlineStr"/>
+      <c r="C703" t="inlineStr"/>
       <c r="D703" t="inlineStr">
         <is>
           <t>ISACTIVATED#Z6#SMS#101</t>
@@ -44367,21 +40387,9 @@
       </c>
     </row>
     <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C704" t="inlineStr">
-        <is>
-          <t>SOB CONFIRMACIÓN</t>
-        </is>
-      </c>
+      <c r="A704" t="inlineStr"/>
+      <c r="B704" t="inlineStr"/>
+      <c r="C704" t="inlineStr"/>
       <c r="D704" t="inlineStr">
         <is>
           <t>NOACTIVE#Z6#SMS#101</t>
@@ -44419,21 +40427,9 @@
       </c>
     </row>
     <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RETENCION TC </t>
-        </is>
-      </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C705" t="inlineStr">
-        <is>
-          <t>TARJETA DE CREDITO</t>
-        </is>
-      </c>
+      <c r="A705" t="inlineStr"/>
+      <c r="B705" t="inlineStr"/>
+      <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr">
         <is>
           <t>ACTIVE#RET#SMS#200</t>
@@ -44471,21 +40467,9 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>DENEGACIONES</t>
-        </is>
-      </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C706" t="inlineStr">
-        <is>
-          <t>SOB CONFIRMACIÓN</t>
-        </is>
-      </c>
+      <c r="A706" t="inlineStr"/>
+      <c r="B706" t="inlineStr"/>
+      <c r="C706" t="inlineStr"/>
       <c r="D706" t="inlineStr">
         <is>
           <t>ACTIVE#BCE#SMS#300</t>

--- a/data/resultado.xlsx
+++ b/data/resultado.xlsx
@@ -6567,7 +6567,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Incrementa tu línea hasta en {S} y planea tu siguiente viaje. &lt;b&gt;Hazlo aquí&lt;/b&gt;.</t>
+          <t>Incrementa la línea de tu Tarjeta de Crédito hoy a {S} y participa del sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>¡Potencia tu Tarjeta de Crédito!</t>
+          <t>¡Un iPhone 17 Pro Max te espera!</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Incrementa tu línea hasta en {S} y planea tu siguiente viaje. &lt;b&gt;Hazlo aquí&lt;/b&gt;.</t>
+          <t>Incrementa la línea de tu Tarjeta de Crédito hoy a {S} y participa del sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>¡Potencia tu Tarjeta de Crédito!</t>
+          <t>¡Un iPhone 17 Pro Max te espera!</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Multiplica tus opciones y gana el Premio Soñado con tu Cuenta Millonaria. Ábrela hoy. TyC.​</t>
+          <t>Abre hoy tu Cuenta Millonaria y participa. A mayor ahorro más opciones de ganar. TyC.</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>¡Depa + auto + viaje!</t>
+          <t>Gana uno de los 4 depas</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Multiplica tus opciones y gana el Premio Soñado con tu Cuenta Millonaria. Ábrela hoy. TyC.​</t>
+          <t>Abre hoy tu Cuenta Millonaria y participa. A mayor ahorro más opciones de ganar. TyC.</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>¡Depa + auto + viaje!</t>
+          <t>Gana uno de los 4 depas</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pidiendo tu Tarjeta de Crédito Adicional. Hazlo aquí. Aplica TyC</t>
+          <t>Solo obtén una Tarjeta de Crédito adicional y participa del sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Ofertas y promociones</t>
+          <t>¡Un iPhone 17 Pro Max para ti!</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pidiendo tu Tarjeta de Crédito Adicional. Hazlo aquí. Aplica TyC</t>
+          <t>Solo obtén una Tarjeta de Crédito adicional y participa del sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H107" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Ofertas y promociones</t>
+          <t>¡Un iPhone 17 Pro Max para ti!</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>"Abre hoy tu Cuenta Súper Tasa desde S/5,000 y elige uno ¡sin sorteos! Inicia &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
+          <t>Abre tu Cuenta Súper Tasa y gana una mejor tasa junto a un premio. Inicia aquí. TyC.</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>"¡Audífonos, Cafetera, Waflera o más!"</t>
+          <t>¡Hasta 4.8% TREA + un premio!</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
+          <t>"Obtén hoy S/{S} con una tasa exclusiva, es rápido y 100% digital. Hazlo aquí&gt;. TyC."</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>¡Tu Extracash puede llevarte a México!</t>
+          <t>¡Tu Extracash espera por ti!</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
+          <t>"Obtén hoy S/{S} con una tasa exclusiva, es rápido y 100% digital. Hazlo aquí&gt;. TyC."</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>¡Tu Extracash puede llevarte a México!</t>
+          <t>¡Tu Extracash espera por ti!</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
+          <t>"Obtén hoy S/{S} con una tasa exclusiva, es rápido y 100% digital. Hazlo aquí&gt;. TyC."</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>¡Tu Extracash puede llevarte a México!</t>
+          <t>¡Tu Extracash espera por ti!</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>"Obtén tu oferta de S/{S} con una mejora de tasa y participa por S/10,000. TyC"</t>
+          <t>"Obtén hoy S/{S} con una tasa mejorada, es rápido y 100% digital. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>¡Tu Préstamo puede llevarte a México!</t>
+          <t>¡Tu Préstamo espera por ti!</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>"Obtén tu oferta de S/{S} con una mejora de tasa y participa por S/10,000. TyC"</t>
+          <t>"Obtén hoy S/{S} con una tasa mejorada, es rápido y 100% digital. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>¡Tu Préstamo puede llevarte a México!</t>
+          <t>¡Tu Préstamo espera por ti!</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>"Obtén tu oferta de S/{S} con una mejora de tasa y participa por S/10,000. TyC"</t>
+          <t>"Obtén hoy S/{S} con una tasa mejorada, es rápido y 100% digital. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>¡Tu Préstamo puede llevarte a México!</t>
+          <t>¡Tu Préstamo espera por ti!</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>"Obtén tu nueva Tarjeta de Crédito, úsala y gana. TyC. Hazlo &lt;b&gt;aquí&lt;/b&gt;."</t>
+          <t>"Obtén tu nueva Tarjeta de Crédito, úsala y gana. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>"Obtén tu nueva Tarjeta de Crédito, úsala y gana. TyC. Hazlo &lt;b&gt;aquí&lt;/b&gt;."</t>
+          <t>"Obtén tu nueva Tarjeta de Crédito, úsala y gana. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>"Con tu nueva Tarjeta de Crédito con {S} de línea, obtenla y úsala hoy. Pídela aquí. TyC."</t>
+          <t>"Obtén tu nueva Tarjeta de Crédito, úsala y gana. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H122" t="n">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>¡S/500 de devolución!</t>
+          <t>¡Hasta S/300 listos para ti!</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Este mes accede a una mejor Tarjeta de Crédito. &lt;b&gt;Obtenla aquí.&lt;/b&gt;</t>
+          <t>Abre hoy tu Cuenta Millonaria y participa. A mayor ahorro más opciones de ganar. TyC.</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>¡Upgrade de Tarjeta activado!</t>
+          <t>Gana uno de los 4 depas</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Incrementa tu línea hasta en {S} y consume con tu Tarjeta para ganar. &lt;b&gt;Hazlo aquí&lt;/b&gt;. TyC.</t>
+          <t>Incrementa tu línea hasta en {S} y consume con tu Tarjeta para ganar. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H152" t="n">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>"Abre hoy tu Depósito a Plazo desde S/15,000 y elige uno ¡sin sorteos! Inicia &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
+          <t>"Abre hoy tu Depósito a Plazo desde S/15,000 y elige uno ¡sin sorteos! Inicia aquí. TyC."</t>
         </is>
       </c>
       <c r="H157" t="n">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pidiendo tu Tarjeta de Crédito Adicional. Hazlo aquí. Aplica TyC</t>
+          <t>Solo obtén una Tarjeta de Crédito adicional y participa del sorteo. Hazlo aquí. TyC.</t>
         </is>
       </c>
       <c r="H160" t="n">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>Ofertas y promociones</t>
+          <t>¡Un iPhone 17 Pro Max para ti!</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>"Abre hoy tu Cuenta Súper Tasa desde S/15,000 y elige uno ¡sin sorteos! Inicia &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
+          <t>Abre tu Cuenta Súper Tasa y gana una mejor tasa junto a un premio. Inicia aquí. TyC.</t>
         </is>
       </c>
       <c r="H161" t="n">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>"¡Alexa, Smartwatch, Maleta o más!"</t>
+          <t>¡Hasta 4.8% TREA + un premio!</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Desembolsa tu oferta de S/{S} y participa en el sorteo. Hazlo aquí. TyC.</t>
+          <t>"Obtén hoy S/{S} con una tasa exclusiva, es rápido y 100% digital. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H164" t="n">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>¡Tu Extracash puede llevarte a México!</t>
+          <t>¡Tu Extracash espera por ti!</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>"Obtén tu oferta de S/{S} con una mejora de tasa y participa por S/10,000. TyC"</t>
+          <t>"Obtén hoy S/{S} con una tasa mejorada, es rápido y 100% digital. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H165" t="n">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>¡Tu Préstamo puede llevarte a México!</t>
+          <t>¡Tu Préstamo espera por ti!</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>"Por tiempo limitado, obtén una Tarjeta de Crédito, úsala y gana sin sorteos. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
+          <t>"Obtén tu nueva Tarjeta de Crédito, úsala y gana. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H167" t="n">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>¡Hasta S/600 pueden ser tuyos!</t>
+          <t>¡Hasta S/300 pueden ser tuyos!</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>"Por tiempo limitado, obtén una Tarjeta de Crédito, úsala y gana sin sorteos. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
+          <t>"Obtén tu nueva Tarjeta de Crédito, úsala y gana. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H168" t="n">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>¡Hasta S/600 pueden ser tuyos!</t>
+          <t>¡Hasta S/300 pueden ser tuyos!</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>"Con tu nueva Tarjeta de Crédito con {S} de línea, obtenla y úsala hoy. Pídela aquí. TyC."</t>
+          <t>"Obtén tu nueva Tarjeta de Crédito, úsala y gana. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H169" t="n">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>¡S/500 de devolución!</t>
+          <t>¡Hasta S/300 pueden ser tuyos!</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>"Tienes una mejora de tu Tarjeta de Crédito, obtenla hoy y participa. Hazlo &lt;b&gt;aquí&lt;/b&gt;. TyC."</t>
+          <t>"Tienes una mejora de tu Tarjeta de Crédito, obtenla hoy y participa. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H176" t="n">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Incrementa tu Línea AQUÍ y participa en el sorteo hasta el 31/05. TyC. 🎁</t>
+          <t>Solicita HOY un Incremento de Línea y entra al sorteo. Aplican TyC.</t>
         </is>
       </c>
       <c r="H201" t="n">
@@ -13996,7 +13996,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/42961fe8-23df-4a14-b019-f9f993255955.png</t>
+          <t>https://content-us-2.content-cms.com/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/dxdam/df/df6d89db-c208-4d4e-9ce9-3938203ae724/modulo_banner_azul_iphone17-1_tcgl_202606.png</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>Participa por un iPhone 17 Pro Max</t>
+          <t>Participa por un iPhone 17 Pro Max 😎</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Incrementa la línea de tu Tarjeta  y disfruta de más beneficios.</t>
+          <t>Incrementa AQUÍ la línea de tu Tarjeta  y entra al sorteo. TyC.</t>
         </is>
       </c>
       <c r="H202" t="n">
@@ -14064,7 +14064,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/42961fe8-23df-4a14-b019-f9f993255955.png</t>
+          <t>https://content-us-2.content-cms.com/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/dxdam/df/df6d89db-c208-4d4e-9ce9-3938203ae724/modulo_banner_azul_iphone17-1_tcgl_202606.png</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>Incrementa tu Línea hoy 💳</t>
+          <t>Un iPhone 17 Pro Max te espera 🎁</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Amplia tu línea de crédito a S/ {S}</t>
+          <t>Solo incrementa tu línea y participa por un iPhone 17 Pro Max. TyC.</t>
         </is>
       </c>
       <c r="H203" t="n">
@@ -14132,7 +14132,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/42961fe8-23df-4a14-b019-f9f993255955.png</t>
+          <t>https://content-us-2.content-cms.com/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/dxdam/df/df6d89db-c208-4d4e-9ce9-3938203ae724/modulo_banner_azul_iphone17-1_tcgl_202606.png</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>Incremento de línea</t>
+          <t>Lo mejor de Apple para ti 📱</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Accede hasta S/ {S} en segundos y disfrútala. Aplican TyC.</t>
+          <t>Solicita tu Incremento de Línea AQUÍ y entra al sorteo hasta el 30/6. TyC.</t>
         </is>
       </c>
       <c r="H204" t="n">
@@ -14200,7 +14200,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/42961fe8-23df-4a14-b019-f9f993255955.png</t>
+          <t>https://content-us-2.content-cms.com/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/dxdam/df/df6d89db-c208-4d4e-9ce9-3938203ae724/modulo_banner_azul_iphone17-1_tcgl_202606.png</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>Incrementa tu línea hoy 💳</t>
+          <t>Últimos días para ganar el iPhone 17</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Accede hasta S/ {S} en segundos y disfrútala. Aplican TyC.</t>
+          <t>Solicítalo hoy 100% digital y disfruta de más beneficios. Hazlo aquí.</t>
         </is>
       </c>
       <c r="H205" t="n">
@@ -14268,7 +14268,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/42961fe8-23df-4a14-b019-f9f993255955.png</t>
+          <t>https://content-us-2.content-cms.com/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/dxdam/df/df6d89db-c208-4d4e-9ce9-3938203ae724/modulo_banner_azul_iphone17-1_tcgl_202606.png</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>Incrementa tu línea hoy 💳</t>
+          <t>Incrementa tu línea HOY 🚀</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Solo mejora tu tarjeta HOY y entra al sorteo. Aplican TyC.</t>
+          <t>Solicita HOY una mejora de tarjeta y participa del sorteo. TyC.</t>
         </is>
       </c>
       <c r="H242" t="n">
@@ -16772,7 +16772,7 @@
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/42961fe8-23df-4a14-b019-f9f993255955.png</t>
+          <t>https://content-us-2.content-cms.com/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/dxdam/5c/5ca80396-26b6-4ee8-acfd-f295332d8264/modulo_banner_azul_iphone17-1_upg_202606.png</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -16786,7 +16786,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>Llévate un iPhone 17 Pro Max 😎</t>
+          <t>"📱 Llévate un iPhone 17 Pro Max "</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Hazlo AQUÍ y participa por un iPhone 17 Pro Max. TyC.</t>
+          <t>Mejora tu tarjeta AQUÍ y entra al sorteo. Válido hasta el 30/6.  TyC.</t>
         </is>
       </c>
       <c r="H243" t="n">
@@ -16840,7 +16840,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/42961fe8-23df-4a14-b019-f9f993255955.png</t>
+          <t>https://content-us-2.content-cms.com/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/dxdam/5c/5ca80396-26b6-4ee8-acfd-f295332d8264/modulo_banner_azul_iphone17-1_upg_202606.png</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>Mejora tu Tarjeta ⬆️🚀</t>
+          <t>Estrena un iPhone 17 Pro Max 😎</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Mejora tu tarjeta HOY y entra al sorteo de un iPhone 17 Pro Max. TyC.</t>
+          <t>Hazlo y entra al sorteo por un iPhone 17 Pro Max. Aplican TyC.</t>
         </is>
       </c>
       <c r="H244" t="n">
@@ -16908,7 +16908,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/42961fe8-23df-4a14-b019-f9f993255955.png</t>
+          <t>https://content-us-2.content-cms.com/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/dxdam/5c/5ca80396-26b6-4ee8-acfd-f295332d8264/modulo_banner_azul_iphone17-1_upg_202606.png</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>Pasa a otro nivel 📈</t>
+          <t>Mejora tu tarjeta HOY  📱🤩</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
@@ -16930,9 +16930,7 @@
           <t>interbank://internal/te-ofrecemos/upgrade/onboarding</t>
         </is>
       </c>
-      <c r="P244" t="n">
-        <v>3</v>
-      </c>
+      <c r="P244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -16967,7 +16965,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Realiza la mejora y disfruta más desde hoy 😎</t>
+          <t>"Pídela AQUÍ y multiplica tus beneficios: promos, dsctos. y más."</t>
         </is>
       </c>
       <c r="H245" t="n">
@@ -16976,7 +16974,7 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t>https://content-us-1.static.content-cms.com/s3/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/42961fe8-23df-4a14-b019-f9f993255955.png</t>
+          <t>https://content-us-2.content-cms.com/9b3f67ef-5a9f-4acc-8ce8-bcc27fa681c7/dxdam/5c/5ca80396-26b6-4ee8-acfd-f295332d8264/modulo_banner_azul_iphone17-1_upg_202606.png</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -16990,7 +16988,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>Sube de nivel tu Tarjeta ⬆️💳</t>
+          <t>Tienes una mejora de tarjeta 😉🚀</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -17167,7 +17165,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Empieza a construir tu futuro financiero. Pídela aquí.</t>
+          <t>Recibe una devolución de S/50 por tu primera compra. Aplican TyC.</t>
         </is>
       </c>
       <c r="H248" t="n">
@@ -17190,7 +17188,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>Tarjeta de Crédito con Garantía</t>
+          <t>Pide HOY tu Tarjeta de Crédito con Garantía Líquida</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">

--- a/data/resultado.xlsx
+++ b/data/resultado.xlsx
@@ -6103,7 +6103,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>"¡Hazlo hoy con el Seguro Premium y obtén una cobertura de hasta S/49,000!"</t>
+          <t>"Protege tus tarjetas Interbank y de otros bancos por hasta S/24,500"</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>"Obtén hoy S/{S} con una tasa mejorada, es rápido y 100% digital. Hazlo aquí. TyC."</t>
+          <t>"Obtén S/{S} hoy de forma rápida y segura, y participa en el sorteo por la tasa promocional. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>¡Tu Préstamo espera por ti!</t>
+          <t>Tu préstamo con 1% TCEA</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>"Obtén hoy S/{S} con una tasa mejorada, es rápido y 100% digital. Hazlo aquí. TyC."</t>
+          <t>"Obtén S/{S} hoy de forma rápida y segura, y participa en el sorteo por la tasa promocional. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>¡Tu Préstamo espera por ti!</t>
+          <t>Tu préstamo con 1% TCEA</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>"Obtén hoy S/{S} con una tasa mejorada, es rápido y 100% digital. Hazlo aquí. TyC."</t>
+          <t>"Obtén S/{S} hoy de forma rápida y segura, y participa en el sorteo por la tasa promocional. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>¡Tu Préstamo espera por ti!</t>
+          <t>Tu préstamo con 1% TCEA</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>"¡Hazlo hoy con el Seguro Premium y obtén una cobertura de hasta S/49,000!"</t>
+          <t>"Protege tus tarjetas Interbank y de otros bancos por hasta S/24,500"</t>
         </is>
       </c>
       <c r="H146" t="n">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>"Obtén hoy S/{S} con una tasa mejorada, es rápido y 100% digital. Hazlo aquí. TyC."</t>
+          <t>"Obtén S/{S} hoy de forma rápida y segura, y participa en el sorteo por la tasa promocional. Hazlo aquí. TyC."</t>
         </is>
       </c>
       <c r="H165" t="n">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>¡Tu Préstamo espera por ti!</t>
+          <t>Tu préstamo con 1% TCEA</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>"¡Hazlo hoy con el Seguro Premium y obtén una cobertura de hasta S/49,000!"</t>
+          <t>"Protege tus tarjetas Interbank y de otros bancos por hasta S/24,500"</t>
         </is>
       </c>
       <c r="H195" t="n">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>"Ábrela y abona desde S/1,500 para el sorteo del depa en febrero."</t>
+          <t>Abre tu Cuenta Millonaria desde S/500 y participa. Primer sorteo este 24 de julio. TyC.</t>
         </is>
       </c>
       <c r="H209" t="n">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>Cuenta Millonaria</t>
+          <t>🏡 ¡Gana uno de los 4 depas!</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>"Ábrela y abona desde S/1,500 para el sorteo del depa en febrero 💚"</t>
+          <t>Abre tu Cuenta Millonaria desde S/500 y participa. Primer sorteo este 24 de julio. TyC.</t>
         </is>
       </c>
       <c r="H210" t="n">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>Cuenta Millonaria</t>
+          <t>🏡 ¡Gana uno de los 4 depas!</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>"¡Todos los meses! Ahorra y gana más de 20,000 premios sin sorteos. Pulsa aquí"</t>
+          <t>Abre tu Cuenta Millonaria desde S/500 y participa. Primer sorteo este 24 de julio. TyC.</t>
         </is>
       </c>
       <c r="H265" t="n">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>Cuenta Millonaria</t>
+          <t>🏡 ¡Gana uno de los 4 depas!</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">

--- a/data/resultado.xlsx
+++ b/data/resultado.xlsx
@@ -10014,7 +10014,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>#2C675F</t>
+          <t>#00463F</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
